--- a/BSMA_AI_Run_Validation1.xlsx
+++ b/BSMA_AI_Run_Validation1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2A399-DBC8-4AE9-A99B-79E24DE02EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65627B51-A546-4C7E-9AFD-5C6E7343D288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5579" uniqueCount="3605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="3606">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -6802,6 +6802,9 @@
     <t>MJ Jayaram</t>
   </si>
   <si>
+    <t>Project-level analysis measuring team/firm-level integration practices via a key informant, not individual-level boundary spanning behavior.. Verbatim Evidence: "[Research Methods] "The unit of analysis for this research was a new product development project. Firms from a variety of industries were selected in order to test for contingency relationships across different settings. Data collection was conducted using a survey instrument. The ideal respondent for the survey was specified to be “the person with overall responsibility for overseeing product development projects”." [Appendix A: Survey Instrument] "The following questions ask about the different practices used by your company in supplier integration, design-manufacturing integration, customer integration, and concurrent process management.""</t>
+  </si>
+  <si>
     <t>BSMA0424</t>
   </si>
   <si>
@@ -6931,7 +6934,7 @@
     <t>Munari, Federico; Righi, Hérica Morais; Toschi, Laura</t>
   </si>
   <si>
-    <t>Excluded due to multiple reasons [Code 1, Code 2, Code 3]: The study uses bibliometric data (projects, publications, patents) rather than surveying individual employees, the unit of analysis is the research project, and it measures project interdisciplinarity rather than interpersonal boundary spanning behavior.. Verbatim Evidence: "Excluded due to multiple reasons [Code 1, Code 2, Code 3]. Verbatim Evidence: "[Abstract] To investigate this issue, we examine 6081 research projects in the Life Sciences, Physical &amp; Engineering, and Social Sciences &amp; Humanities sectors funded by the European Research Council under the 7th Framework Programme and Horizon 2020 Programme in the period 2008–2016." "[Data and methods] We used a database built following the approach recently explored by the innovation literature which refers to research projects’ contribution to the development of patents by tracing the patent citations to scientific publications (Azoulay et al., 2019; Fleming et al., 2019; Li et al., 2017)." "[Measures] To obtain the degree of boundary spanning of each project, we used one measure of boundary spanning research indicated in the literature: variety... We calculated this variable as the total number of unique subject areas of all the backward citations reported in the publications of each project.""</t>
+    <t>Bibliometric and project-level analysis [Code 2 &amp; Code 3]. Verbatim Evidence: "[Bibliometric and project-level analysis]. Verbatim Evidence: "[Abstract] To investigate this issue, we examine 6081 research projects in the Life Sciences, Physical &amp; Engineering, and Social Sciences &amp; Humanities sectors funded by the European Research Council under the 7th Framework Programme and Horizon 2020 Programme in the period 2008–2016." "[5.2. Measures] We calculated this variable as the total number of unique subject areas of all the backward citations reported in the publications of each project.""</t>
   </si>
   <si>
     <t>BSMA0432</t>
@@ -20799,7 +20802,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20895,7 +20898,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20991,7 +20994,7 @@
         <v>2010</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="11" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21055,7 +21058,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21087,7 +21090,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21375,7 +21378,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21503,7 +21506,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21535,7 +21538,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21567,7 +21570,7 @@
         <v>2018</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21695,7 +21698,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21823,7 +21826,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21919,7 +21922,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21983,7 +21986,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22207,7 +22210,7 @@
         <v>2010</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22335,7 +22338,7 @@
         <v>2019</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22399,7 +22402,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22431,7 +22434,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22527,7 +22530,7 @@
         <v>2005</v>
       </c>
       <c r="P58" s="8" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22591,7 +22594,7 @@
         <v>1997</v>
       </c>
       <c r="P60" s="8" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22879,7 +22882,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23071,7 +23074,7 @@
         <v>1993</v>
       </c>
       <c r="P75" s="8" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23103,7 +23106,7 @@
         <v>2022</v>
       </c>
       <c r="P76" s="8" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23135,7 +23138,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23167,7 +23170,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23199,7 +23202,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23263,7 +23266,7 @@
         <v>2009</v>
       </c>
       <c r="P81" s="8" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23327,7 +23330,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23359,7 +23362,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23391,7 +23394,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23487,7 +23490,7 @@
         <v>2022</v>
       </c>
       <c r="P88" s="8" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23519,7 +23522,7 @@
         <v>2008</v>
       </c>
       <c r="P89" s="8" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23583,7 +23586,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3466</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23615,7 +23618,7 @@
         <v>2026</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>3467</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23679,7 +23682,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3468</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23711,7 +23714,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3469</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23807,7 +23810,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3470</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23871,7 +23874,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3471</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23967,7 +23970,7 @@
         <v>2016</v>
       </c>
       <c r="P103" s="8" t="s">
-        <v>3472</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23999,7 +24002,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3473</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24223,7 +24226,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3474</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24319,7 +24322,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3475</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24383,7 +24386,7 @@
         <v>2010</v>
       </c>
       <c r="P116" s="8" t="s">
-        <v>3476</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24543,7 +24546,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3477</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24607,7 +24610,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3478</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24735,7 +24738,7 @@
         <v>1989</v>
       </c>
       <c r="P127" s="8" t="s">
-        <v>3479</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24767,7 +24770,7 @@
         <v>1999</v>
       </c>
       <c r="P128" s="8" t="s">
-        <v>3480</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24863,7 +24866,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3481</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24895,7 +24898,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3482</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25087,7 +25090,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3483</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25183,7 +25186,7 @@
         <v>2014</v>
       </c>
       <c r="P141" s="8" t="s">
-        <v>3484</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25311,7 +25314,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3485</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25343,7 +25346,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3486</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25407,7 +25410,7 @@
         <v>2025</v>
       </c>
       <c r="P148" s="8" t="s">
-        <v>3487</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25503,7 +25506,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3488</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25631,7 +25634,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3489</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25663,7 +25666,7 @@
         <v>2021</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>3490</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25695,7 +25698,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3491</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25727,7 +25730,7 @@
         <v>2030</v>
       </c>
       <c r="P158" s="8" t="s">
-        <v>3492</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25759,7 +25762,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3493</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25823,7 +25826,7 @@
         <v>2022</v>
       </c>
       <c r="P161" s="8" t="s">
-        <v>3494</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25983,7 +25986,7 @@
         <v>1992</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>3495</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26015,7 +26018,7 @@
         <v>2012</v>
       </c>
       <c r="P167" s="8" t="s">
-        <v>3496</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26111,7 +26114,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3497</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26335,7 +26338,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3498</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26399,7 +26402,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3499</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26431,7 +26434,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3500</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26559,7 +26562,7 @@
         <v>2019</v>
       </c>
       <c r="P184" s="8" t="s">
-        <v>3501</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26623,7 +26626,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3502</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26655,7 +26658,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3503</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26847,7 +26850,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26943,7 +26946,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3505</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27039,7 +27042,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3506</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27167,7 +27170,7 @@
         <v>2010</v>
       </c>
       <c r="P203" s="8" t="s">
-        <v>3507</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="204" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27199,7 +27202,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3508</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27295,7 +27298,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3509</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27327,7 +27330,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3510</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27391,7 +27394,7 @@
         <v>2022</v>
       </c>
       <c r="P210" s="8" t="s">
-        <v>3511</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="211" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27423,7 +27426,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3512</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27455,7 +27458,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3513</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27487,7 +27490,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3514</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27551,7 +27554,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3515</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27679,7 +27682,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3516</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27711,7 +27714,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3517</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27807,7 +27810,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3518</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27871,7 +27874,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3519</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27903,7 +27906,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27999,7 +28002,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3521</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28031,7 +28034,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3522</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28127,7 +28130,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3523</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28191,7 +28194,7 @@
         <v>2013</v>
       </c>
       <c r="P235" s="8" t="s">
-        <v>3524</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="236" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28223,7 +28226,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3525</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28287,7 +28290,7 @@
         <v>2021</v>
       </c>
       <c r="P238" s="8" t="s">
-        <v>3526</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="239" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28383,7 +28386,7 @@
         <v>2019</v>
       </c>
       <c r="P241" s="8" t="s">
-        <v>3527</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="242" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28447,7 +28450,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3528</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28479,7 +28482,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3529</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28511,7 +28514,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3530</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28703,7 +28706,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3531</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28863,7 +28866,7 @@
         <v>2008</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>3532</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="257" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28895,7 +28898,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3533</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28959,7 +28962,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3534</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29119,7 +29122,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3535</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29183,7 +29186,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3536</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29247,7 +29250,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3537</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29279,7 +29282,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3538</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29375,7 +29378,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3539</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29471,7 +29474,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3540</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29599,7 +29602,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3541</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29663,7 +29666,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3542</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29759,7 +29762,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3543</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29791,7 +29794,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3544</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29983,7 +29986,7 @@
         <v>1981</v>
       </c>
       <c r="P291" s="8" t="s">
-        <v>3545</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30207,7 +30210,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3546</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30239,7 +30242,7 @@
         <v>2018</v>
       </c>
       <c r="P299" s="8" t="s">
-        <v>3547</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30367,7 +30370,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3548</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30431,7 +30434,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3549</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30495,7 +30498,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3550</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30527,7 +30530,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3551</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30559,7 +30562,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3552</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30815,7 +30818,7 @@
         <v>2018</v>
       </c>
       <c r="P317" s="8" t="s">
-        <v>3553</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30911,7 +30914,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3554</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30943,7 +30946,7 @@
         <v>2000</v>
       </c>
       <c r="P321" s="8" t="s">
-        <v>3555</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30975,7 +30978,7 @@
         <v>2020</v>
       </c>
       <c r="P322" s="8" t="s">
-        <v>3556</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="323" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31039,7 +31042,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3557</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31071,7 +31074,7 @@
         <v>2011</v>
       </c>
       <c r="P325" s="8" t="s">
-        <v>3558</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="326" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31103,7 +31106,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3559</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31167,7 +31170,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3560</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31359,7 +31362,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3561</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31391,7 +31394,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3562</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31423,7 +31426,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3563</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31551,7 +31554,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3564</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31583,7 +31586,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3565</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31615,7 +31618,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3566</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31647,7 +31650,7 @@
         <v>2007</v>
       </c>
       <c r="P343" s="8" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="344" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31679,7 +31682,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3568</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31711,7 +31714,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3569</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31743,7 +31746,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3570</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31775,7 +31778,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31935,7 +31938,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3572</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31999,7 +32002,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3573</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32031,7 +32034,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3574</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32063,7 +32066,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32188,7 +32191,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32252,7 +32255,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3577</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32284,7 +32287,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3578</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32476,7 +32479,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3579</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32572,7 +32575,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3580</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32924,7 +32927,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3581</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32956,7 +32959,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3582</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33084,7 +33087,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3583</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33116,7 +33119,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3584</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33180,7 +33183,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3585</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33212,7 +33215,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3586</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33436,7 +33439,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3587</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33468,7 +33471,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3588</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33500,7 +33503,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3589</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33532,7 +33535,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3590</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33596,7 +33599,7 @@
         <v>2022</v>
       </c>
       <c r="P404" s="8" t="s">
-        <v>3591</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="405" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33628,7 +33631,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3592</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33660,7 +33663,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3593</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33692,7 +33695,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3594</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33852,7 +33855,7 @@
         <v>2011</v>
       </c>
       <c r="P412" s="8" t="s">
-        <v>3595</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="413" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33916,7 +33919,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3596</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34076,7 +34079,7 @@
         <v>2016</v>
       </c>
       <c r="P419" s="8" t="s">
-        <v>3597</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="420" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34140,7 +34143,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3598</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34278,6 +34281,12 @@
       <c r="B426" t="s">
         <v>2219</v>
       </c>
+      <c r="E426" t="s">
+        <v>45</v>
+      </c>
+      <c r="F426" t="s">
+        <v>46</v>
+      </c>
       <c r="G426" t="s">
         <v>2220</v>
       </c>
@@ -34293,14 +34302,16 @@
       <c r="K426">
         <v>1998</v>
       </c>
-      <c r="P426" s="8"/>
+      <c r="P426" s="8" t="s">
+        <v>2223</v>
+      </c>
     </row>
     <row r="427" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A427" t="s">
         <v>43</v>
       </c>
       <c r="B427" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="E427" t="s">
         <v>45</v>
@@ -34309,22 +34320,22 @@
         <v>52</v>
       </c>
       <c r="G427" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="H427" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="I427" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="J427" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="K427">
         <v>1977</v>
       </c>
       <c r="P427" s="8" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="428" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34332,7 +34343,7 @@
         <v>43</v>
       </c>
       <c r="B428" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="E428" t="s">
         <v>45</v>
@@ -34341,22 +34352,22 @@
         <v>114</v>
       </c>
       <c r="G428" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="H428" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="I428" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="J428" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="K428">
         <v>2023</v>
       </c>
       <c r="P428" s="8" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="429" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34364,7 +34375,7 @@
         <v>43</v>
       </c>
       <c r="B429" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E429" t="s">
         <v>45</v>
@@ -34373,22 +34384,22 @@
         <v>46</v>
       </c>
       <c r="G429" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="H429" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="I429" t="s">
         <v>469</v>
       </c>
       <c r="J429" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="K429">
         <v>1994</v>
       </c>
       <c r="P429" s="8" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="430" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34396,7 +34407,7 @@
         <v>43</v>
       </c>
       <c r="B430" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="E430" t="s">
         <v>45</v>
@@ -34405,22 +34416,22 @@
         <v>114</v>
       </c>
       <c r="G430" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="H430" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="I430" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="J430" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="K430">
         <v>2025</v>
       </c>
       <c r="P430" s="8" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="431" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34428,7 +34439,7 @@
         <v>43</v>
       </c>
       <c r="B431" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="E431" t="s">
         <v>45</v>
@@ -34437,22 +34448,22 @@
         <v>52</v>
       </c>
       <c r="G431" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="H431" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="I431" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="J431" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="K431">
         <v>1996</v>
       </c>
       <c r="P431" s="8" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="432" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34460,7 +34471,7 @@
         <v>43</v>
       </c>
       <c r="B432" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="E432" t="s">
         <v>45</v>
@@ -34469,22 +34480,22 @@
         <v>52</v>
       </c>
       <c r="G432" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="H432" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="I432" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="J432" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="K432">
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3599</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34492,7 +34503,7 @@
         <v>43</v>
       </c>
       <c r="B433" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="E433" t="s">
         <v>45</v>
@@ -34501,22 +34512,22 @@
         <v>52</v>
       </c>
       <c r="G433" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="H433" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="I433" t="s">
         <v>348</v>
       </c>
       <c r="J433" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="K433">
         <v>1998</v>
       </c>
       <c r="P433" s="8" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="434" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34524,7 +34535,7 @@
         <v>43</v>
       </c>
       <c r="B434" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="E434" t="s">
         <v>45</v>
@@ -34533,22 +34544,22 @@
         <v>52</v>
       </c>
       <c r="G434" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="H434" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="I434" t="s">
         <v>1436</v>
       </c>
       <c r="J434" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="K434">
         <v>2025</v>
       </c>
       <c r="P434" s="8" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="435" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34556,7 +34567,7 @@
         <v>43</v>
       </c>
       <c r="B435" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="E435" t="s">
         <v>45</v>
@@ -34565,22 +34576,22 @@
         <v>52</v>
       </c>
       <c r="G435" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="H435" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="I435" t="s">
         <v>495</v>
       </c>
       <c r="J435" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="K435">
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3600</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34588,7 +34599,7 @@
         <v>43</v>
       </c>
       <c r="B436" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="E436" t="s">
         <v>45</v>
@@ -34597,22 +34608,22 @@
         <v>52</v>
       </c>
       <c r="G436" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="H436" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="I436" t="s">
         <v>771</v>
       </c>
       <c r="J436" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="K436">
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3601</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34620,7 +34631,7 @@
         <v>43</v>
       </c>
       <c r="B437" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="E437" t="s">
         <v>45</v>
@@ -34629,22 +34640,22 @@
         <v>46</v>
       </c>
       <c r="G437" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="H437" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="I437" t="s">
         <v>49</v>
       </c>
       <c r="J437" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="K437">
         <v>1989</v>
       </c>
       <c r="P437" s="8" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="438" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34652,7 +34663,7 @@
         <v>43</v>
       </c>
       <c r="B438" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="E438" t="s">
         <v>45</v>
@@ -34661,22 +34672,22 @@
         <v>52</v>
       </c>
       <c r="G438" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="H438" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="I438" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="J438" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="K438">
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3602</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34684,7 +34695,7 @@
         <v>43</v>
       </c>
       <c r="B439" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="E439" t="s">
         <v>45</v>
@@ -34693,22 +34704,22 @@
         <v>46</v>
       </c>
       <c r="G439" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="H439" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="I439" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="J439" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="K439">
         <v>2017</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="440" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34716,7 +34727,7 @@
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="E440" t="s">
         <v>45</v>
@@ -34725,22 +34736,22 @@
         <v>52</v>
       </c>
       <c r="G440" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="H440" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="I440" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="J440" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="K440">
         <v>1998</v>
       </c>
       <c r="P440" s="8" t="s">
-        <v>3603</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="441" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34748,7 +34759,7 @@
         <v>43</v>
       </c>
       <c r="B441" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="E441" t="s">
         <v>45</v>
@@ -34757,22 +34768,22 @@
         <v>52</v>
       </c>
       <c r="G441" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="H441" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="I441" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="J441" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="K441">
         <v>2020</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="442" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34780,7 +34791,7 @@
         <v>43</v>
       </c>
       <c r="B442" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="E442" t="s">
         <v>45</v>
@@ -34789,22 +34800,22 @@
         <v>114</v>
       </c>
       <c r="G442" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="H442" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="I442" t="s">
         <v>49</v>
       </c>
       <c r="J442" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="K442">
         <v>2020</v>
       </c>
       <c r="P442" s="8" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="443" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34812,7 +34823,7 @@
         <v>43</v>
       </c>
       <c r="B443" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="E443" t="s">
         <v>45</v>
@@ -34821,22 +34832,22 @@
         <v>52</v>
       </c>
       <c r="G443" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="H443" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="I443" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="J443" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="K443">
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3604</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34844,19 +34855,19 @@
         <v>43</v>
       </c>
       <c r="B444" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="G444" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="H444" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="I444" t="s">
         <v>698</v>
       </c>
       <c r="J444" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="K444">
         <v>2002</v>
@@ -34868,19 +34879,19 @@
         <v>43</v>
       </c>
       <c r="B445" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="G445" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="H445" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="I445" t="s">
         <v>49</v>
       </c>
       <c r="J445" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="K445">
         <v>2013</v>
@@ -34892,19 +34903,19 @@
         <v>43</v>
       </c>
       <c r="B446" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="G446" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="H446" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="I446" t="s">
         <v>258</v>
       </c>
       <c r="J446" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="K446">
         <v>2023</v>
@@ -34916,19 +34927,19 @@
         <v>43</v>
       </c>
       <c r="B447" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="G447" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="H447" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="I447" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="J447" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="K447">
         <v>2013</v>
@@ -34940,19 +34951,19 @@
         <v>43</v>
       </c>
       <c r="B448" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="G448" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="H448" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="I448" t="s">
         <v>1789</v>
       </c>
       <c r="J448" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="K448">
         <v>2022</v>
@@ -34964,19 +34975,19 @@
         <v>43</v>
       </c>
       <c r="B449" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="G449" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="H449" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="I449" t="s">
         <v>2190</v>
       </c>
       <c r="J449" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="K449">
         <v>2016</v>
@@ -34988,19 +34999,19 @@
         <v>43</v>
       </c>
       <c r="B450" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="G450" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="H450" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="I450" t="s">
         <v>1896</v>
       </c>
       <c r="J450" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="K450">
         <v>2010</v>
@@ -35012,19 +35023,19 @@
         <v>43</v>
       </c>
       <c r="B451" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="G451" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="H451" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="I451" t="s">
         <v>49</v>
       </c>
       <c r="J451" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="K451">
         <v>2013</v>
@@ -35036,19 +35047,19 @@
         <v>43</v>
       </c>
       <c r="B452" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="G452" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="H452" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="I452" t="s">
         <v>287</v>
       </c>
       <c r="J452" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="K452">
         <v>2008</v>
@@ -35060,19 +35071,19 @@
         <v>43</v>
       </c>
       <c r="B453" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="G453" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="H453" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="I453" t="s">
         <v>677</v>
       </c>
       <c r="J453" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="K453">
         <v>2007</v>
@@ -35084,19 +35095,19 @@
         <v>43</v>
       </c>
       <c r="B454" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="G454" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="H454" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="I454" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="J454" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="K454">
         <v>2003</v>
@@ -35108,19 +35119,19 @@
         <v>43</v>
       </c>
       <c r="B455" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="G455" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="H455" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="I455" t="s">
         <v>2159</v>
       </c>
       <c r="J455" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="K455">
         <v>2024</v>
@@ -35132,19 +35143,19 @@
         <v>43</v>
       </c>
       <c r="B456" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="G456" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H456" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="I456" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="J456" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="K456">
         <v>2022</v>
@@ -35156,19 +35167,19 @@
         <v>43</v>
       </c>
       <c r="B457" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="G457" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="H457" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="I457" t="s">
         <v>213</v>
       </c>
       <c r="J457" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="K457">
         <v>2019</v>
@@ -35180,19 +35191,19 @@
         <v>43</v>
       </c>
       <c r="B458" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="G458" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="H458" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="I458" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="J458" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="K458">
         <v>2024</v>
@@ -35204,19 +35215,19 @@
         <v>43</v>
       </c>
       <c r="B459" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="G459" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="H459" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="I459" t="s">
         <v>895</v>
       </c>
       <c r="J459" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="K459">
         <v>2003</v>
@@ -35228,19 +35239,19 @@
         <v>43</v>
       </c>
       <c r="B460" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="G460" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="H460" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="I460" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="J460" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="K460">
         <v>2024</v>
@@ -35252,19 +35263,19 @@
         <v>43</v>
       </c>
       <c r="B461" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="G461" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="H461" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="I461" t="s">
         <v>49</v>
       </c>
       <c r="J461" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="K461">
         <v>2023</v>
@@ -35276,19 +35287,19 @@
         <v>43</v>
       </c>
       <c r="B462" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="G462" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="H462" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="I462" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="J462" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="K462">
         <v>1995</v>
@@ -35300,19 +35311,19 @@
         <v>43</v>
       </c>
       <c r="B463" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="G463" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="H463" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="I463" t="s">
         <v>49</v>
       </c>
       <c r="J463" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="K463">
         <v>1989</v>
@@ -35324,19 +35335,19 @@
         <v>43</v>
       </c>
       <c r="B464" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="G464" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="H464" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="I464" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="J464" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="K464">
         <v>1996</v>
@@ -35348,19 +35359,19 @@
         <v>43</v>
       </c>
       <c r="B465" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="G465" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="H465" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="I465" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="J465" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="K465">
         <v>2021</v>
@@ -35372,19 +35383,19 @@
         <v>43</v>
       </c>
       <c r="B466" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="G466" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="H466" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="I466" t="s">
         <v>123</v>
       </c>
       <c r="J466" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="K466">
         <v>2017</v>
@@ -35396,19 +35407,19 @@
         <v>43</v>
       </c>
       <c r="B467" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="G467" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="H467" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="I467" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="J467" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="K467">
         <v>2023</v>
@@ -35420,19 +35431,19 @@
         <v>43</v>
       </c>
       <c r="B468" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="G468" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="H468" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="I468" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J468" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="K468">
         <v>2012</v>
@@ -35444,19 +35455,19 @@
         <v>43</v>
       </c>
       <c r="B469" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="G469" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="H469" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="I469" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="J469" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="K469">
         <v>2021</v>
@@ -35468,19 +35479,19 @@
         <v>43</v>
       </c>
       <c r="B470" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="G470" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="H470" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="I470" t="s">
         <v>399</v>
       </c>
       <c r="J470" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="K470">
         <v>2022</v>
@@ -35492,19 +35503,19 @@
         <v>43</v>
       </c>
       <c r="B471" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="G471" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="H471" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="I471" t="s">
         <v>49</v>
       </c>
       <c r="J471" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="K471">
         <v>2018</v>
@@ -35516,19 +35527,19 @@
         <v>43</v>
       </c>
       <c r="B472" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="G472" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="H472" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="I472" t="s">
         <v>49</v>
       </c>
       <c r="J472" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="K472">
         <v>2021</v>
@@ -35540,19 +35551,19 @@
         <v>43</v>
       </c>
       <c r="B473" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="G473" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="H473" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="I473" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="J473" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="K473">
         <v>1982</v>
@@ -35564,19 +35575,19 @@
         <v>43</v>
       </c>
       <c r="B474" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="G474" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="H474" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="I474" t="s">
         <v>2030</v>
       </c>
       <c r="J474" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="K474">
         <v>2014</v>
@@ -35588,19 +35599,19 @@
         <v>43</v>
       </c>
       <c r="B475" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="G475" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="H475" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="I475" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="J475" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="K475">
         <v>2005</v>
@@ -35612,19 +35623,19 @@
         <v>43</v>
       </c>
       <c r="B476" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="G476" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="H476" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="I476" t="s">
         <v>1626</v>
       </c>
       <c r="J476" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="K476">
         <v>2011</v>
@@ -35636,19 +35647,19 @@
         <v>43</v>
       </c>
       <c r="B477" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="G477" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="H477" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="I477" t="s">
         <v>299</v>
       </c>
       <c r="J477" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="K477">
         <v>1979</v>
@@ -35660,19 +35671,19 @@
         <v>43</v>
       </c>
       <c r="B478" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="G478" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="H478" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="I478" t="s">
         <v>1289</v>
       </c>
       <c r="J478" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="K478">
         <v>1985</v>
@@ -35684,19 +35695,19 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="G479" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="H479" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="I479" t="s">
         <v>1831</v>
       </c>
       <c r="J479" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="K479">
         <v>2011</v>
@@ -35708,19 +35719,19 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="G480" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="H480" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="I480" t="s">
         <v>77</v>
       </c>
       <c r="J480" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="K480">
         <v>1976</v>
@@ -35732,19 +35743,19 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="G481" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="H481" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="I481" t="s">
         <v>709</v>
       </c>
       <c r="J481" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="K481">
         <v>2006</v>
@@ -35756,19 +35767,19 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="G482" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="H482" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="I482" t="s">
         <v>2159</v>
       </c>
       <c r="J482" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="K482">
         <v>2001</v>
@@ -35780,19 +35791,19 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="G483" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="H483" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="I483" t="s">
         <v>49</v>
       </c>
       <c r="J483" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="K483">
         <v>2020</v>
@@ -35804,19 +35815,19 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="G484" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="H484" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="I484" t="s">
         <v>1334</v>
       </c>
       <c r="J484" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="K484">
         <v>2013</v>
@@ -35828,19 +35839,19 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="G485" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="H485" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="I485" t="s">
         <v>287</v>
       </c>
       <c r="J485" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="K485">
         <v>2012</v>
@@ -35852,19 +35863,19 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="G486" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="H486" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="I486" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="J486" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="K486">
         <v>1996</v>
@@ -35876,19 +35887,19 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="G487" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="H487" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="I487" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="J487" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="K487">
         <v>1995</v>
@@ -35900,19 +35911,19 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="G488" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="H488" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="I488" t="s">
         <v>49</v>
       </c>
       <c r="J488" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="K488">
         <v>2002</v>
@@ -35924,19 +35935,19 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="G489" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H489" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="I489" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="J489" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="K489">
         <v>2023</v>
@@ -35948,19 +35959,19 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="G490" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="H490" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="I490" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="J490" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="K490">
         <v>2011</v>
@@ -35972,19 +35983,19 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
+        <v>2515</v>
+      </c>
+      <c r="G491" t="s">
+        <v>2516</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2517</v>
+      </c>
+      <c r="I491" t="s">
+        <v>2518</v>
+      </c>
+      <c r="J491" t="s">
         <v>2514</v>
-      </c>
-      <c r="G491" t="s">
-        <v>2515</v>
-      </c>
-      <c r="H491" t="s">
-        <v>2516</v>
-      </c>
-      <c r="I491" t="s">
-        <v>2517</v>
-      </c>
-      <c r="J491" t="s">
-        <v>2513</v>
       </c>
       <c r="K491">
         <v>2011</v>
@@ -35996,19 +36007,19 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="G492" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="H492" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="I492" t="s">
         <v>49</v>
       </c>
       <c r="J492" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="K492">
         <v>1984</v>
@@ -36020,19 +36031,19 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="G493" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="H493" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="I493" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="J493" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="K493">
         <v>2017</v>
@@ -36044,19 +36055,19 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="G494" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="H494" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="I494" t="s">
         <v>1702</v>
       </c>
       <c r="J494" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="K494">
         <v>2025</v>
@@ -36068,19 +36079,19 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="G495" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="H495" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="I495" t="s">
         <v>628</v>
       </c>
       <c r="J495" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="K495">
         <v>2025</v>
@@ -36092,19 +36103,19 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="G496" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="H496" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="I496" t="s">
         <v>299</v>
       </c>
       <c r="J496" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="K496">
         <v>2020</v>
@@ -36116,19 +36127,19 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="G497" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="H497" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="I497" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="J497" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="K497">
         <v>2019</v>
@@ -36140,19 +36151,19 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="G498" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="H498" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="I498" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="J498" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="K498">
         <v>2023</v>
@@ -36164,19 +36175,19 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="G499" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="H499" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="I499" t="s">
         <v>671</v>
       </c>
       <c r="J499" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="K499">
         <v>2001</v>
@@ -36188,19 +36199,19 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="G500" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="H500" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="I500" t="s">
         <v>709</v>
       </c>
       <c r="J500" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="K500">
         <v>2022</v>
@@ -36212,19 +36223,19 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="G501" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="H501" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="I501" t="s">
         <v>245</v>
       </c>
       <c r="J501" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="K501">
         <v>2001</v>
@@ -36236,19 +36247,19 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="G502" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="H502" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="I502" t="s">
         <v>299</v>
       </c>
       <c r="J502" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="K502">
         <v>1976</v>
@@ -36260,19 +36271,19 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="G503" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="H503" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="I503" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="J503" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="K503">
         <v>1981</v>
@@ -36284,19 +36295,19 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="G504" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="H504" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="I504" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="J504" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="K504">
         <v>2025</v>
@@ -36308,19 +36319,19 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="G505" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="H505" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="I505" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="J505" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="K505">
         <v>1998</v>
@@ -36332,19 +36343,19 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="G506" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="H506" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="I506" t="s">
         <v>342</v>
       </c>
       <c r="J506" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="K506">
         <v>2010</v>
@@ -36356,19 +36367,19 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="G507" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="H507" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="I507" t="s">
         <v>1993</v>
       </c>
       <c r="J507" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="K507">
         <v>2016</v>
@@ -36380,19 +36391,19 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="G508" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="H508" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="I508" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="J508" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="K508">
         <v>2004</v>
@@ -36404,19 +36415,19 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="G509" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="H509" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="I509" t="s">
         <v>469</v>
       </c>
       <c r="J509" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="K509">
         <v>1989</v>
@@ -36428,19 +36439,19 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="G510" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="H510" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="I510" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="J510" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="K510">
         <v>2005</v>
@@ -36452,19 +36463,19 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="G511" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="H511" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="I511" t="s">
         <v>393</v>
       </c>
       <c r="J511" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="K511">
         <v>2025</v>
@@ -36476,19 +36487,19 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="G512" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="H512" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="I512" t="s">
         <v>1626</v>
       </c>
       <c r="J512" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="K512">
         <v>2018</v>
@@ -36500,19 +36511,19 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="G513" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="H513" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="I513" t="s">
         <v>1474</v>
       </c>
       <c r="J513" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="K513">
         <v>2011</v>
@@ -36524,19 +36535,19 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="G514" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="H514" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="I514" t="s">
         <v>1218</v>
       </c>
       <c r="J514" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="K514">
         <v>2024</v>
@@ -36548,19 +36559,19 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="G515" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="H515" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="I515" t="s">
         <v>1753</v>
       </c>
       <c r="J515" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="K515">
         <v>2023</v>
@@ -36572,19 +36583,19 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="G516" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="H516" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="I516" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="J516" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="K516">
         <v>2010</v>
@@ -36596,19 +36607,19 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="G517" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="H517" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="I517" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="J517" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="K517">
         <v>2019</v>
@@ -36620,19 +36631,19 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="G518" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="H518" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="I518" t="s">
         <v>49</v>
       </c>
       <c r="J518" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="K518">
         <v>1986</v>
@@ -36644,19 +36655,19 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="G519" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="H519" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="I519" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="J519" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="K519">
         <v>2018</v>
@@ -36668,19 +36679,19 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="G520" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="H520" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="I520" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="J520" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="K520">
         <v>2006</v>
@@ -36692,19 +36703,19 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="G521" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="H521" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="I521" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="J521" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -36716,19 +36727,19 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="G522" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="H522" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="I522" t="s">
         <v>1172</v>
       </c>
       <c r="J522" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -36740,19 +36751,19 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="G523" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="H523" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="I523" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="J523" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -36764,19 +36775,19 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="G524" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="H524" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="I524" t="s">
         <v>1702</v>
       </c>
       <c r="J524" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -36788,19 +36799,19 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="G525" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="H525" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="I525" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="J525" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -36812,19 +36823,19 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="G526" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="H526" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="I526" t="s">
         <v>321</v>
       </c>
       <c r="J526" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -36836,19 +36847,19 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="G527" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="H527" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="I527" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="J527" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -36860,19 +36871,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="G528" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="H528" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="I528" t="s">
         <v>1369</v>
       </c>
       <c r="J528" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -36884,19 +36895,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="G529" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="H529" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="I529" t="s">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="J529" t="s">
-        <v>2685</v>
+        <v>2686</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -36908,19 +36919,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="G530" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="H530" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="I530" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="J530" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -36932,19 +36943,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="G531" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="H531" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="I531" t="s">
         <v>534</v>
       </c>
       <c r="J531" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -36956,19 +36967,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="G532" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="H532" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="I532" t="s">
         <v>94</v>
       </c>
       <c r="J532" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -36980,19 +36991,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="G533" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="H533" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="I533" t="s">
         <v>148</v>
       </c>
       <c r="J533" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -37004,19 +37015,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="G534" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="H534" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="I534" t="s">
         <v>671</v>
       </c>
       <c r="J534" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -37028,19 +37039,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="G535" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="H535" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="I535" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="J535" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -37052,19 +37063,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="G536" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="H536" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="I536" t="s">
         <v>638</v>
       </c>
       <c r="J536" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -37076,19 +37087,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="G537" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="H537" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="I537" t="s">
         <v>416</v>
       </c>
       <c r="J537" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -37100,19 +37111,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="G538" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="H538" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="I538" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="J538" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -37124,19 +37135,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="G539" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="H539" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="I539" t="s">
         <v>348</v>
       </c>
       <c r="J539" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -37148,19 +37159,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="G540" t="s">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="H540" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="I540" t="s">
         <v>49</v>
       </c>
       <c r="J540" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -37172,19 +37183,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="G541" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="H541" t="s">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="I541" t="s">
         <v>299</v>
       </c>
       <c r="J541" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -37196,19 +37207,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="G542" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="H542" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="I542" t="s">
         <v>230</v>
       </c>
       <c r="J542" t="s">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -37220,19 +37231,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="G543" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="H543" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="I543" t="s">
         <v>337</v>
       </c>
       <c r="J543" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -37244,19 +37255,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="G544" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="H544" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="I544" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="J544" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -37268,19 +37279,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="G545" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="H545" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="I545" t="s">
         <v>881</v>
       </c>
       <c r="J545" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -37292,19 +37303,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2754</v>
+        <v>2755</v>
       </c>
       <c r="G546" t="s">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="H546" t="s">
-        <v>2756</v>
+        <v>2757</v>
       </c>
       <c r="I546" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="J546" t="s">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -37316,19 +37327,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="G547" t="s">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="H547" t="s">
-        <v>2760</v>
+        <v>2761</v>
       </c>
       <c r="I547" t="s">
         <v>258</v>
       </c>
       <c r="J547" t="s">
-        <v>2761</v>
+        <v>2762</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -37340,19 +37351,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="G548" t="s">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="H548" t="s">
-        <v>2764</v>
+        <v>2765</v>
       </c>
       <c r="I548" t="s">
         <v>709</v>
       </c>
       <c r="J548" t="s">
-        <v>2765</v>
+        <v>2766</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -37364,19 +37375,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2766</v>
+        <v>2767</v>
       </c>
       <c r="G549" t="s">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="H549" t="s">
-        <v>2768</v>
+        <v>2769</v>
       </c>
       <c r="I549" t="s">
         <v>49</v>
       </c>
       <c r="J549" t="s">
-        <v>2769</v>
+        <v>2770</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -37388,19 +37399,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2770</v>
+        <v>2771</v>
       </c>
       <c r="G550" t="s">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="H550" t="s">
-        <v>2772</v>
+        <v>2773</v>
       </c>
       <c r="I550" t="s">
         <v>142</v>
       </c>
       <c r="J550" t="s">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -37412,19 +37423,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
-        <v>2774</v>
+        <v>2775</v>
       </c>
       <c r="G551" t="s">
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="H551" t="s">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="I551" t="s">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="J551" t="s">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -37436,19 +37447,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="G552" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="H552" t="s">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="I552" t="s">
-        <v>2782</v>
+        <v>2783</v>
       </c>
       <c r="J552" t="s">
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -37460,19 +37471,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="G553" t="s">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="H553" t="s">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="I553" t="s">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="J553" t="s">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -37484,19 +37495,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="G554" t="s">
-        <v>2790</v>
+        <v>2791</v>
       </c>
       <c r="H554" t="s">
-        <v>2791</v>
+        <v>2792</v>
       </c>
       <c r="I554" t="s">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="J554" t="s">
-        <v>2793</v>
+        <v>2794</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -37508,19 +37519,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="G555" t="s">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="H555" t="s">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="I555" t="s">
         <v>416</v>
       </c>
       <c r="J555" t="s">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -37532,19 +37543,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="G556" t="s">
-        <v>2799</v>
+        <v>2800</v>
       </c>
       <c r="H556" t="s">
-        <v>2800</v>
+        <v>2801</v>
       </c>
       <c r="I556" t="s">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="J556" t="s">
-        <v>2802</v>
+        <v>2803</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -37556,19 +37567,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="G557" t="s">
-        <v>2804</v>
+        <v>2805</v>
       </c>
       <c r="H557" t="s">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="I557" t="s">
         <v>348</v>
       </c>
       <c r="J557" t="s">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -37580,19 +37591,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="G558" t="s">
-        <v>2808</v>
+        <v>2809</v>
       </c>
       <c r="H558" t="s">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="I558" t="s">
         <v>230</v>
       </c>
       <c r="J558" t="s">
-        <v>2810</v>
+        <v>2811</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -37604,19 +37615,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="G559" t="s">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="H559" t="s">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="I559" t="s">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="J559" t="s">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -37628,19 +37639,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="G560" t="s">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="H560" t="s">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="I560" t="s">
         <v>992</v>
       </c>
       <c r="J560" t="s">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -37652,19 +37663,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="G561" t="s">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="H561" t="s">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="I561" t="s">
         <v>49</v>
       </c>
       <c r="J561" t="s">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -37676,19 +37687,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="G562" t="s">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="H562" t="s">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="I562" t="s">
         <v>49</v>
       </c>
       <c r="J562" t="s">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -37700,19 +37711,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2828</v>
+        <v>2829</v>
       </c>
       <c r="G563" t="s">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="H563" t="s">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="I563" t="s">
         <v>49</v>
       </c>
       <c r="J563" t="s">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -37724,19 +37735,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="G564" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="H564" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="I564" t="s">
         <v>1436</v>
       </c>
       <c r="J564" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -37748,19 +37759,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="G565" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="H565" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="I565" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="J565" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -37772,19 +37783,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="G566" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="H566" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="I566" t="s">
         <v>449</v>
       </c>
       <c r="J566" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -37796,19 +37807,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="G567" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="H567" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="I567" t="s">
         <v>895</v>
       </c>
       <c r="J567" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -37820,19 +37831,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="G568" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="H568" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="I568" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="J568" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -37844,19 +37855,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="G569" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="H569" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="I569" t="s">
         <v>49</v>
       </c>
       <c r="J569" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -37868,19 +37879,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="G570" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="H570" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="I570" t="s">
         <v>49</v>
       </c>
       <c r="J570" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -37892,19 +37903,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="G571" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="H571" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="I571" t="s">
         <v>957</v>
       </c>
       <c r="J571" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -37916,19 +37927,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="G572" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="H572" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="I572" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="J572" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -37940,19 +37951,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="G573" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="H573" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="I573" t="s">
         <v>677</v>
       </c>
       <c r="J573" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -37964,19 +37975,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="G574" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="H574" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="I574" t="s">
         <v>49</v>
       </c>
       <c r="J574" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -37988,19 +37999,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="G575" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="H575" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="I575" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="J575" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -38012,19 +38023,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="G576" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="H576" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="I576" t="s">
         <v>709</v>
       </c>
       <c r="J576" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -38036,19 +38047,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="G577" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="H577" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="I577" t="s">
         <v>895</v>
       </c>
       <c r="J577" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -38060,19 +38071,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="G578" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="H578" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="I578" t="s">
         <v>709</v>
       </c>
       <c r="J578" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -38084,19 +38095,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="G579" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="H579" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="I579" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="J579" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -38108,19 +38119,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="G580" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="H580" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="I580" t="s">
         <v>245</v>
       </c>
       <c r="J580" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -38132,19 +38143,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="G581" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="H581" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="I581" t="s">
         <v>709</v>
       </c>
       <c r="J581" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -38156,19 +38167,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="G582" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="H582" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="I582" t="s">
         <v>190</v>
       </c>
       <c r="J582" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -38180,19 +38191,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="G583" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="H583" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="I583" t="s">
         <v>2159</v>
       </c>
       <c r="J583" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -38204,19 +38215,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="G584" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="H584" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="I584" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="J584" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -38228,19 +38239,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="G585" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="H585" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="I585" t="s">
         <v>729</v>
       </c>
       <c r="J585" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -38252,19 +38263,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="G586" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="H586" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="I586" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="J586" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -38276,19 +38287,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="G587" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="H587" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="I587" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="J587" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -38300,19 +38311,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="G588" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="H588" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="I588" t="s">
         <v>1334</v>
       </c>
       <c r="J588" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -38324,19 +38335,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="G589" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="H589" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="I589" t="s">
         <v>957</v>
       </c>
       <c r="J589" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -38348,19 +38359,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="G590" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="H590" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="I590" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="J590" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -38372,19 +38383,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="G591" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="H591" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="I591" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="J591" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -38396,19 +38407,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="G592" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="H592" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="I592" t="s">
         <v>2159</v>
       </c>
       <c r="J592" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -38420,19 +38431,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="G593" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="H593" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="I593" t="s">
         <v>2019</v>
       </c>
       <c r="J593" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -38444,19 +38455,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="G594" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="H594" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="I594" t="s">
         <v>968</v>
       </c>
       <c r="J594" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -38468,19 +38479,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="G595" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="H595" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="I595" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="J595" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -38492,19 +38503,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="G596" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="H596" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="I596" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="J596" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -38516,19 +38527,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="G597" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="H597" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="I597" t="s">
         <v>49</v>
       </c>
       <c r="J597" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -38540,19 +38551,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="G598" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="H598" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="I598" t="s">
         <v>1284</v>
       </c>
       <c r="J598" t="s">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -38564,19 +38575,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="G599" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="H599" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="I599" t="s">
         <v>1626</v>
       </c>
       <c r="J599" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -38588,19 +38599,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="G600" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="H600" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="I600" t="s">
         <v>49</v>
       </c>
       <c r="J600" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -38612,19 +38623,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="G601" t="s">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="H601" t="s">
-        <v>2992</v>
+        <v>2993</v>
       </c>
       <c r="I601" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="J601" t="s">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -38636,19 +38647,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="G602" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="H602" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="I602" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="J602" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -38660,19 +38671,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="G603" t="s">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="H603" t="s">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="I603" t="s">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="J603" t="s">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -38684,19 +38695,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="G604" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="H604" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="I604" t="s">
         <v>94</v>
       </c>
       <c r="J604" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -38708,19 +38719,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="G605" t="s">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="H605" t="s">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="I605" t="s">
         <v>1896</v>
       </c>
       <c r="J605" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -38732,19 +38743,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="G606" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="H606" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="I606" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="J606" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -38756,19 +38767,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="G607" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="H607" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="I607" t="s">
         <v>1495</v>
       </c>
       <c r="J607" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -38780,19 +38791,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="G608" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="H608" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="I608" t="s">
         <v>1495</v>
       </c>
       <c r="J608" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -38804,19 +38815,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="G609" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="H609" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="I609" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="J609" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -38828,19 +38839,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="G610" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="H610" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="I610" t="s">
         <v>219</v>
       </c>
       <c r="J610" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -38852,19 +38863,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="G611" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="H611" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="I611" t="s">
         <v>219</v>
       </c>
       <c r="J611" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -38876,19 +38887,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="G612" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="H612" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="I612" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="J612" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -38900,19 +38911,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="G613" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="H613" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="I613" t="s">
         <v>1388</v>
       </c>
       <c r="J613" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -38924,19 +38935,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G614" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="H614" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="I614" t="s">
         <v>399</v>
       </c>
       <c r="J614" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -38948,19 +38959,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="G615" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="H615" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="I615" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="J615" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -38972,19 +38983,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="G616" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="H616" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="I616" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="J616" t="s">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -38996,19 +39007,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="G617" t="s">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="H617" t="s">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="I617" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="J617" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -39020,19 +39031,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="G618" t="s">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="H618" t="s">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="I618" t="s">
         <v>287</v>
       </c>
       <c r="J618" t="s">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -39044,19 +39055,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="G619" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="H619" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="I619" t="s">
         <v>895</v>
       </c>
       <c r="J619" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -39068,19 +39079,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="G620" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="H620" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="I620" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="J620" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -39092,19 +39103,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="G621" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="H621" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="I621" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="J621" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -39116,19 +39127,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="G622" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="H622" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="I622" t="s">
         <v>951</v>
       </c>
       <c r="J622" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -39140,19 +39151,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="G623" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="H623" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="I623" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="J623" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -39164,19 +39175,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="G624" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="H624" t="s">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="I624" t="s">
         <v>1626</v>
       </c>
       <c r="J624" t="s">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -39188,19 +39199,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="G625" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="H625" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="I625" t="s">
         <v>1218</v>
       </c>
       <c r="J625" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -39212,19 +39223,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="G626" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="H626" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="I626" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="J626" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -39236,19 +39247,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="G627" t="s">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="H627" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="I627" t="s">
         <v>123</v>
       </c>
       <c r="J627" t="s">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -39260,19 +39271,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="G628" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="H628" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="I628" t="s">
         <v>895</v>
       </c>
       <c r="J628" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -39284,19 +39295,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="G629" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="H629" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="I629" t="s">
         <v>1626</v>
       </c>
       <c r="J629" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -39308,19 +39319,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="G630" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="H630" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="I630" t="s">
         <v>677</v>
       </c>
       <c r="J630" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -39332,19 +39343,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="G631" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="H631" t="s">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="I631" t="s">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="J631" t="s">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -39356,19 +39367,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="G632" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="H632" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="I632" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="J632" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -39380,19 +39391,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="G633" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="H633" t="s">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="I633" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="J633" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -39404,19 +39415,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="G634" t="s">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="H634" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="I634" t="s">
         <v>219</v>
       </c>
       <c r="J634" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -39428,19 +39439,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="G635" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="H635" t="s">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="I635" t="s">
         <v>809</v>
       </c>
       <c r="J635" t="s">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -39452,19 +39463,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="G636" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="H636" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="I636" t="s">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="J636" t="s">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -39476,19 +39487,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="G637" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="H637" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="I637" t="s">
         <v>287</v>
       </c>
       <c r="J637" t="s">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -39500,19 +39511,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="G638" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="H638" t="s">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="I638" t="s">
         <v>287</v>
       </c>
       <c r="J638" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -39524,19 +39535,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="G639" t="s">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="H639" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="I639" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="J639" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -39548,19 +39559,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="G640" t="s">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="H640" t="s">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="I640" t="s">
         <v>219</v>
       </c>
       <c r="J640" t="s">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -39572,19 +39583,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="G641" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="H641" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="I641" t="s">
         <v>1524</v>
       </c>
       <c r="J641" t="s">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -39596,19 +39607,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="G642" t="s">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="H642" t="s">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="I642" t="s">
         <v>534</v>
       </c>
       <c r="J642" t="s">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -39620,19 +39631,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="G643" t="s">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="H643" t="s">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="I643" t="s">
         <v>142</v>
       </c>
       <c r="J643" t="s">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -39644,19 +39655,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="G644" t="s">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="H644" t="s">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="I644" t="s">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="J644" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -39668,19 +39679,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="G645" t="s">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="H645" t="s">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="I645" t="s">
         <v>1284</v>
       </c>
       <c r="J645" t="s">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -39692,19 +39703,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="G646" t="s">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="H646" t="s">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="I646" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="J646" t="s">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -39716,19 +39727,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="G647" t="s">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="H647" t="s">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="I647" t="s">
         <v>287</v>
       </c>
       <c r="J647" t="s">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -39740,19 +39751,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="G648" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="H648" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="I648" t="s">
         <v>1626</v>
       </c>
       <c r="J648" t="s">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -39764,19 +39775,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="G649" t="s">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="H649" t="s">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="I649" t="s">
         <v>399</v>
       </c>
       <c r="J649" t="s">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -39788,19 +39799,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="G650" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="H650" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="I650" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="J650" t="s">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -39812,19 +39823,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="G651" t="s">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="H651" t="s">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="I651" t="s">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="J651" t="s">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -39836,19 +39847,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="G652" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="H652" t="s">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="I652" t="s">
         <v>1310</v>
       </c>
       <c r="J652" t="s">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -39860,19 +39871,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="G653" t="s">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="H653" t="s">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="I653" t="s">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="J653" t="s">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -39884,19 +39895,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="G654" t="s">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="H654" t="s">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="I654" t="s">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="J654" t="s">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -39908,19 +39919,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="G655" t="s">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="H655" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="I655" t="s">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="J655" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -39932,19 +39943,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="G656" t="s">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="H656" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="I656" t="s">
         <v>677</v>
       </c>
       <c r="J656" t="s">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -39956,19 +39967,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="G657" t="s">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="H657" t="s">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="I657" t="s">
         <v>2030</v>
       </c>
       <c r="J657" t="s">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -39980,19 +39991,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="G658" t="s">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="H658" t="s">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="I658" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="J658" t="s">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -40004,19 +40015,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="G659" t="s">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="H659" t="s">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="I659" t="s">
         <v>1960</v>
       </c>
       <c r="J659" t="s">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -40028,19 +40039,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="G660" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="H660" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="I660" t="s">
         <v>49</v>
       </c>
       <c r="J660" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -40052,19 +40063,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="G661" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="H661" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="I661" t="s">
         <v>649</v>
       </c>
       <c r="J661" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -40076,19 +40087,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="G662" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="H662" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="I662" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="J662" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -40100,19 +40111,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="G663" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="H663" t="s">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="I663" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="J663" t="s">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -40124,19 +40135,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="G664" t="s">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="H664" t="s">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="I664" t="s">
         <v>399</v>
       </c>
       <c r="J664" t="s">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -40148,19 +40159,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="G665" t="s">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="H665" t="s">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="I665" t="s">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="J665" t="s">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -40172,19 +40183,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="G666" t="s">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="H666" t="s">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="I666" t="s">
         <v>1388</v>
       </c>
       <c r="J666" t="s">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -40196,19 +40207,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="G667" t="s">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="H667" t="s">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="I667" t="s">
         <v>449</v>
       </c>
       <c r="J667" t="s">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -40220,19 +40231,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="G668" t="s">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="H668" t="s">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="I668" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="J668" t="s">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -40244,19 +40255,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="G669" t="s">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="H669" t="s">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="I669" t="s">
         <v>416</v>
       </c>
       <c r="J669" t="s">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -40268,19 +40279,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="G670" t="s">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="H670" t="s">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="I670" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="J670" t="s">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -40292,19 +40303,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="G671" t="s">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="H671" t="s">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="I671" t="s">
         <v>2211</v>
       </c>
       <c r="J671" t="s">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -40316,19 +40327,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="G672" t="s">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="H672" t="s">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="I672" t="s">
         <v>123</v>
       </c>
       <c r="J672" t="s">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -40340,19 +40351,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="G673" t="s">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="H673" t="s">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="I673" t="s">
         <v>1454</v>
       </c>
       <c r="J673" t="s">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -40364,19 +40375,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="G674" t="s">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="H674" t="s">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="I674" t="s">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="J674" t="s">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -40388,19 +40399,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="G675" t="s">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="H675" t="s">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="I675" t="s">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="J675" t="s">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -40412,19 +40423,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="G676" t="s">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="H676" t="s">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="I676" t="s">
         <v>1648</v>
       </c>
       <c r="J676" t="s">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -40436,19 +40447,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="G677" t="s">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="H677" t="s">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="I677" t="s">
         <v>671</v>
       </c>
       <c r="J677" t="s">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -40460,19 +40471,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="G678" t="s">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="H678" t="s">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="I678" t="s">
         <v>399</v>
       </c>
       <c r="J678" t="s">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -40484,19 +40495,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="G679" t="s">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="H679" t="s">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="I679" t="s">
         <v>49</v>
       </c>
       <c r="J679" t="s">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -40508,19 +40519,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="G680" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="H680" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="I680" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="J680" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -40532,19 +40543,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="G681" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="H681" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="I681" t="s">
         <v>230</v>
       </c>
       <c r="J681" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -40556,19 +40567,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="G682" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="H682" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="I682" t="s">
         <v>1057</v>
       </c>
       <c r="J682" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -40580,19 +40591,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="G683" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="H683" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="I683" t="s">
         <v>230</v>
       </c>
       <c r="J683" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -40604,19 +40615,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="G684" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="H684" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="I684" t="s">
         <v>803</v>
       </c>
       <c r="J684" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -40628,19 +40639,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="G685" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="H685" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="I685" t="s">
         <v>405</v>
       </c>
       <c r="J685" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -40652,19 +40663,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="G686" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="H686" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="I686" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="J686" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -40676,19 +40687,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="G687" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="H687" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="I687" t="s">
         <v>1901</v>
       </c>
       <c r="J687" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -40700,19 +40711,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="G688" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="H688" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="I688" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="J688" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -40724,19 +40735,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="G689" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="H689" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="I689" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="J689" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -40748,19 +40759,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="G690" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="H690" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="I690" t="s">
         <v>393</v>
       </c>
       <c r="J690" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -40772,19 +40783,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="G691" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="H691" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="I691" t="s">
         <v>2019</v>
       </c>
       <c r="J691" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -40796,19 +40807,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="G692" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="H692" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="I692" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="J692" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -40820,19 +40831,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="G693" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="H693" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="I693" t="s">
         <v>230</v>
       </c>
       <c r="J693" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -40844,19 +40855,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="G694" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="H694" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="I694" t="s">
         <v>951</v>
       </c>
       <c r="J694" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -40868,19 +40879,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="G695" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H695" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="I695" t="s">
         <v>1901</v>
       </c>
       <c r="J695" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -40892,19 +40903,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="G696" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="H696" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="I696" t="s">
         <v>951</v>
       </c>
       <c r="J696" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -40916,19 +40927,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G697" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H697" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="I697" t="s">
         <v>1436</v>
       </c>
       <c r="J697" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -40940,19 +40951,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="G698" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="H698" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="I698" t="s">
         <v>709</v>
       </c>
       <c r="J698" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -40964,19 +40975,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="G699" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="H699" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="I699" t="s">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="J699" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -40988,19 +40999,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="G700" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="H700" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="I700" t="s">
         <v>895</v>
       </c>
       <c r="J700" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -41012,19 +41023,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G701" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H701" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="I701" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="J701" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -41036,19 +41047,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="G702" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="H702" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="I702" t="s">
         <v>895</v>
       </c>
       <c r="J702" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -41060,19 +41071,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G703" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H703" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="I703" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="J703" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -41084,19 +41095,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="G704" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="H704" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="I704" t="s">
         <v>49</v>
       </c>
       <c r="J704" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation1.xlsx
+++ b/BSMA_AI_Run_Validation1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65627B51-A546-4C7E-9AFD-5C6E7343D288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5387EA-509D-4C9A-97A3-3857D9A7AC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="3606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5581" uniqueCount="3605">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -6932,9 +6932,6 @@
   </si>
   <si>
     <t>Munari, Federico; Righi, Hérica Morais; Toschi, Laura</t>
-  </si>
-  <si>
-    <t>Bibliometric and project-level analysis [Code 2 &amp; Code 3]. Verbatim Evidence: "[Bibliometric and project-level analysis]. Verbatim Evidence: "[Abstract] To investigate this issue, we examine 6081 research projects in the Life Sciences, Physical &amp; Engineering, and Social Sciences &amp; Humanities sectors funded by the European Research Council under the 7th Framework Programme and Horizon 2020 Programme in the period 2008–2016." "[5.2. Measures] We calculated this variable as the total number of unique subject areas of all the backward citations reported in the publications of each project.""</t>
   </si>
   <si>
     <t>BSMA0432</t>
@@ -20802,7 +20799,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20898,7 +20895,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20994,7 +20991,7 @@
         <v>2010</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="11" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21058,7 +21055,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21090,7 +21087,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21378,7 +21375,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21506,7 +21503,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21538,7 +21535,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21570,7 +21567,7 @@
         <v>2018</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21698,7 +21695,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21826,7 +21823,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21922,7 +21919,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21986,7 +21983,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22210,7 +22207,7 @@
         <v>2010</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22338,7 +22335,7 @@
         <v>2019</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22402,7 +22399,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22434,7 +22431,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22530,7 +22527,7 @@
         <v>2005</v>
       </c>
       <c r="P58" s="8" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22594,7 +22591,7 @@
         <v>1997</v>
       </c>
       <c r="P60" s="8" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22882,7 +22879,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23074,7 +23071,7 @@
         <v>1993</v>
       </c>
       <c r="P75" s="8" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23106,7 +23103,7 @@
         <v>2022</v>
       </c>
       <c r="P76" s="8" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23138,7 +23135,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23170,7 +23167,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23202,7 +23199,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23266,7 +23263,7 @@
         <v>2009</v>
       </c>
       <c r="P81" s="8" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23330,7 +23327,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23362,7 +23359,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23394,7 +23391,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23490,7 +23487,7 @@
         <v>2022</v>
       </c>
       <c r="P88" s="8" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23522,7 +23519,7 @@
         <v>2008</v>
       </c>
       <c r="P89" s="8" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23586,7 +23583,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23618,7 +23615,7 @@
         <v>2026</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23682,7 +23679,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23714,7 +23711,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23810,7 +23807,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23874,7 +23871,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23970,7 +23967,7 @@
         <v>2016</v>
       </c>
       <c r="P103" s="8" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24002,7 +23999,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24226,7 +24223,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24322,7 +24319,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24386,7 +24383,7 @@
         <v>2010</v>
       </c>
       <c r="P116" s="8" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24546,7 +24543,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24610,7 +24607,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24738,7 +24735,7 @@
         <v>1989</v>
       </c>
       <c r="P127" s="8" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24770,7 +24767,7 @@
         <v>1999</v>
       </c>
       <c r="P128" s="8" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24866,7 +24863,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24898,7 +24895,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25090,7 +25087,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25186,7 +25183,7 @@
         <v>2014</v>
       </c>
       <c r="P141" s="8" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25314,7 +25311,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25346,7 +25343,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25410,7 +25407,7 @@
         <v>2025</v>
       </c>
       <c r="P148" s="8" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25506,7 +25503,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25634,7 +25631,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25666,7 +25663,7 @@
         <v>2021</v>
       </c>
       <c r="P156" s="8" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25698,7 +25695,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25730,7 +25727,7 @@
         <v>2030</v>
       </c>
       <c r="P158" s="8" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="159" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25762,7 +25759,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25826,7 +25823,7 @@
         <v>2022</v>
       </c>
       <c r="P161" s="8" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25986,7 +25983,7 @@
         <v>1992</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26018,7 +26015,7 @@
         <v>2012</v>
       </c>
       <c r="P167" s="8" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26114,7 +26111,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26338,7 +26335,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26402,7 +26399,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26434,7 +26431,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26562,7 +26559,7 @@
         <v>2019</v>
       </c>
       <c r="P184" s="8" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26626,7 +26623,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26658,7 +26655,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26850,7 +26847,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26946,7 +26943,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27042,7 +27039,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27170,7 +27167,7 @@
         <v>2010</v>
       </c>
       <c r="P203" s="8" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="204" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27202,7 +27199,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27298,7 +27295,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27330,7 +27327,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27394,7 +27391,7 @@
         <v>2022</v>
       </c>
       <c r="P210" s="8" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="211" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27426,7 +27423,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27458,7 +27455,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27490,7 +27487,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27554,7 +27551,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27682,7 +27679,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27714,7 +27711,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27810,7 +27807,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27874,7 +27871,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27906,7 +27903,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28002,7 +27999,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28034,7 +28031,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28130,7 +28127,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28194,7 +28191,7 @@
         <v>2013</v>
       </c>
       <c r="P235" s="8" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="236" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28226,7 +28223,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28290,7 +28287,7 @@
         <v>2021</v>
       </c>
       <c r="P238" s="8" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="239" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28386,7 +28383,7 @@
         <v>2019</v>
       </c>
       <c r="P241" s="8" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="242" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28450,7 +28447,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28482,7 +28479,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28514,7 +28511,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28706,7 +28703,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28866,7 +28863,7 @@
         <v>2008</v>
       </c>
       <c r="P256" s="8" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="257" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28898,7 +28895,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28962,7 +28959,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29122,7 +29119,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29186,7 +29183,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29250,7 +29247,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29282,7 +29279,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29378,7 +29375,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29474,7 +29471,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29602,7 +29599,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29666,7 +29663,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29762,7 +29759,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29794,7 +29791,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29986,7 +29983,7 @@
         <v>1981</v>
       </c>
       <c r="P291" s="8" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30210,7 +30207,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30242,7 +30239,7 @@
         <v>2018</v>
       </c>
       <c r="P299" s="8" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30370,7 +30367,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30434,7 +30431,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30498,7 +30495,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30530,7 +30527,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30562,7 +30559,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30818,7 +30815,7 @@
         <v>2018</v>
       </c>
       <c r="P317" s="8" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30914,7 +30911,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30946,7 +30943,7 @@
         <v>2000</v>
       </c>
       <c r="P321" s="8" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30978,7 +30975,7 @@
         <v>2020</v>
       </c>
       <c r="P322" s="8" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="323" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31042,7 +31039,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31074,7 +31071,7 @@
         <v>2011</v>
       </c>
       <c r="P325" s="8" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="326" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31106,7 +31103,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31170,7 +31167,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31362,7 +31359,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31394,7 +31391,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31426,7 +31423,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31554,7 +31551,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31586,7 +31583,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31618,7 +31615,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31650,7 +31647,7 @@
         <v>2007</v>
       </c>
       <c r="P343" s="8" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="344" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31682,7 +31679,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31714,7 +31711,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31746,7 +31743,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31778,7 +31775,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31938,7 +31935,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32002,7 +31999,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32034,7 +32031,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32066,7 +32063,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32191,7 +32188,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32255,7 +32252,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32287,7 +32284,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32479,7 +32476,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32575,7 +32572,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32927,7 +32924,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32959,7 +32956,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33087,7 +33084,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33119,7 +33116,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33183,7 +33180,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33215,7 +33212,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33439,7 +33436,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33471,7 +33468,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33503,7 +33500,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33535,7 +33532,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33599,7 +33596,7 @@
         <v>2022</v>
       </c>
       <c r="P404" s="8" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="405" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33631,7 +33628,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33663,7 +33660,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33695,7 +33692,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33855,7 +33852,7 @@
         <v>2011</v>
       </c>
       <c r="P412" s="8" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="413" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33919,7 +33916,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34079,7 +34076,7 @@
         <v>2016</v>
       </c>
       <c r="P419" s="8" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="420" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34143,7 +34140,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34495,7 +34492,7 @@
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34538,10 +34535,7 @@
         <v>2263</v>
       </c>
       <c r="E434" t="s">
-        <v>45</v>
-      </c>
-      <c r="F434" t="s">
-        <v>52</v>
+        <v>1888</v>
       </c>
       <c r="G434" t="s">
         <v>2264</v>
@@ -34559,7 +34553,7 @@
         <v>2025</v>
       </c>
       <c r="P434" s="8" t="s">
-        <v>2267</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="435" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34567,7 +34561,7 @@
         <v>43</v>
       </c>
       <c r="B435" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="E435" t="s">
         <v>45</v>
@@ -34576,22 +34570,22 @@
         <v>52</v>
       </c>
       <c r="G435" t="s">
+        <v>2268</v>
+      </c>
+      <c r="H435" t="s">
         <v>2269</v>
-      </c>
-      <c r="H435" t="s">
-        <v>2270</v>
       </c>
       <c r="I435" t="s">
         <v>495</v>
       </c>
       <c r="J435" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K435">
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34599,7 +34593,7 @@
         <v>43</v>
       </c>
       <c r="B436" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="E436" t="s">
         <v>45</v>
@@ -34608,22 +34602,22 @@
         <v>52</v>
       </c>
       <c r="G436" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H436" t="s">
         <v>2273</v>
-      </c>
-      <c r="H436" t="s">
-        <v>2274</v>
       </c>
       <c r="I436" t="s">
         <v>771</v>
       </c>
       <c r="J436" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="K436">
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34631,7 +34625,7 @@
         <v>43</v>
       </c>
       <c r="B437" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E437" t="s">
         <v>45</v>
@@ -34640,22 +34634,22 @@
         <v>46</v>
       </c>
       <c r="G437" t="s">
+        <v>2276</v>
+      </c>
+      <c r="H437" t="s">
         <v>2277</v>
-      </c>
-      <c r="H437" t="s">
-        <v>2278</v>
       </c>
       <c r="I437" t="s">
         <v>49</v>
       </c>
       <c r="J437" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="K437">
         <v>1989</v>
       </c>
       <c r="P437" s="8" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="438" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34663,7 +34657,7 @@
         <v>43</v>
       </c>
       <c r="B438" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E438" t="s">
         <v>45</v>
@@ -34672,22 +34666,22 @@
         <v>52</v>
       </c>
       <c r="G438" t="s">
+        <v>2281</v>
+      </c>
+      <c r="H438" t="s">
         <v>2282</v>
       </c>
-      <c r="H438" t="s">
+      <c r="I438" t="s">
         <v>2283</v>
       </c>
-      <c r="I438" t="s">
+      <c r="J438" t="s">
         <v>2284</v>
-      </c>
-      <c r="J438" t="s">
-        <v>2285</v>
       </c>
       <c r="K438">
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34695,7 +34689,7 @@
         <v>43</v>
       </c>
       <c r="B439" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E439" t="s">
         <v>45</v>
@@ -34704,22 +34698,22 @@
         <v>46</v>
       </c>
       <c r="G439" t="s">
+        <v>2286</v>
+      </c>
+      <c r="H439" t="s">
         <v>2287</v>
       </c>
-      <c r="H439" t="s">
+      <c r="I439" t="s">
         <v>2288</v>
       </c>
-      <c r="I439" t="s">
+      <c r="J439" t="s">
         <v>2289</v>
-      </c>
-      <c r="J439" t="s">
-        <v>2290</v>
       </c>
       <c r="K439">
         <v>2017</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="440" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34727,7 +34721,7 @@
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="E440" t="s">
         <v>45</v>
@@ -34736,22 +34730,22 @@
         <v>52</v>
       </c>
       <c r="G440" t="s">
+        <v>2292</v>
+      </c>
+      <c r="H440" t="s">
         <v>2293</v>
       </c>
-      <c r="H440" t="s">
+      <c r="I440" t="s">
         <v>2294</v>
       </c>
-      <c r="I440" t="s">
+      <c r="J440" t="s">
         <v>2295</v>
-      </c>
-      <c r="J440" t="s">
-        <v>2296</v>
       </c>
       <c r="K440">
         <v>1998</v>
       </c>
       <c r="P440" s="8" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="441" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34759,7 +34753,7 @@
         <v>43</v>
       </c>
       <c r="B441" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="E441" t="s">
         <v>45</v>
@@ -34768,22 +34762,22 @@
         <v>52</v>
       </c>
       <c r="G441" t="s">
+        <v>2297</v>
+      </c>
+      <c r="H441" t="s">
         <v>2298</v>
       </c>
-      <c r="H441" t="s">
+      <c r="I441" t="s">
         <v>2299</v>
       </c>
-      <c r="I441" t="s">
+      <c r="J441" t="s">
         <v>2300</v>
-      </c>
-      <c r="J441" t="s">
-        <v>2301</v>
       </c>
       <c r="K441">
         <v>2020</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="442" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34791,7 +34785,7 @@
         <v>43</v>
       </c>
       <c r="B442" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="E442" t="s">
         <v>45</v>
@@ -34800,22 +34794,22 @@
         <v>114</v>
       </c>
       <c r="G442" t="s">
+        <v>2303</v>
+      </c>
+      <c r="H442" t="s">
         <v>2304</v>
-      </c>
-      <c r="H442" t="s">
-        <v>2305</v>
       </c>
       <c r="I442" t="s">
         <v>49</v>
       </c>
       <c r="J442" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="K442">
         <v>2020</v>
       </c>
       <c r="P442" s="8" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="443" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34823,7 +34817,7 @@
         <v>43</v>
       </c>
       <c r="B443" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="E443" t="s">
         <v>45</v>
@@ -34832,22 +34826,22 @@
         <v>52</v>
       </c>
       <c r="G443" t="s">
+        <v>2308</v>
+      </c>
+      <c r="H443" t="s">
         <v>2309</v>
       </c>
-      <c r="H443" t="s">
+      <c r="I443" t="s">
         <v>2310</v>
       </c>
-      <c r="I443" t="s">
+      <c r="J443" t="s">
         <v>2311</v>
-      </c>
-      <c r="J443" t="s">
-        <v>2312</v>
       </c>
       <c r="K443">
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34855,19 +34849,19 @@
         <v>43</v>
       </c>
       <c r="B444" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G444" t="s">
         <v>2313</v>
       </c>
-      <c r="G444" t="s">
+      <c r="H444" t="s">
         <v>2314</v>
-      </c>
-      <c r="H444" t="s">
-        <v>2315</v>
       </c>
       <c r="I444" t="s">
         <v>698</v>
       </c>
       <c r="J444" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="K444">
         <v>2002</v>
@@ -34879,19 +34873,19 @@
         <v>43</v>
       </c>
       <c r="B445" t="s">
+        <v>2316</v>
+      </c>
+      <c r="G445" t="s">
         <v>2317</v>
       </c>
-      <c r="G445" t="s">
+      <c r="H445" t="s">
         <v>2318</v>
-      </c>
-      <c r="H445" t="s">
-        <v>2319</v>
       </c>
       <c r="I445" t="s">
         <v>49</v>
       </c>
       <c r="J445" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="K445">
         <v>2013</v>
@@ -34903,19 +34897,19 @@
         <v>43</v>
       </c>
       <c r="B446" t="s">
+        <v>2320</v>
+      </c>
+      <c r="G446" t="s">
         <v>2321</v>
       </c>
-      <c r="G446" t="s">
+      <c r="H446" t="s">
         <v>2322</v>
-      </c>
-      <c r="H446" t="s">
-        <v>2323</v>
       </c>
       <c r="I446" t="s">
         <v>258</v>
       </c>
       <c r="J446" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="K446">
         <v>2023</v>
@@ -34927,19 +34921,19 @@
         <v>43</v>
       </c>
       <c r="B447" t="s">
+        <v>2324</v>
+      </c>
+      <c r="G447" t="s">
         <v>2325</v>
       </c>
-      <c r="G447" t="s">
+      <c r="H447" t="s">
         <v>2326</v>
       </c>
-      <c r="H447" t="s">
+      <c r="I447" t="s">
         <v>2327</v>
       </c>
-      <c r="I447" t="s">
+      <c r="J447" t="s">
         <v>2328</v>
-      </c>
-      <c r="J447" t="s">
-        <v>2329</v>
       </c>
       <c r="K447">
         <v>2013</v>
@@ -34951,19 +34945,19 @@
         <v>43</v>
       </c>
       <c r="B448" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G448" t="s">
         <v>2330</v>
       </c>
-      <c r="G448" t="s">
+      <c r="H448" t="s">
         <v>2331</v>
-      </c>
-      <c r="H448" t="s">
-        <v>2332</v>
       </c>
       <c r="I448" t="s">
         <v>1789</v>
       </c>
       <c r="J448" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="K448">
         <v>2022</v>
@@ -34975,19 +34969,19 @@
         <v>43</v>
       </c>
       <c r="B449" t="s">
+        <v>2333</v>
+      </c>
+      <c r="G449" t="s">
         <v>2334</v>
       </c>
-      <c r="G449" t="s">
+      <c r="H449" t="s">
         <v>2335</v>
-      </c>
-      <c r="H449" t="s">
-        <v>2336</v>
       </c>
       <c r="I449" t="s">
         <v>2190</v>
       </c>
       <c r="J449" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="K449">
         <v>2016</v>
@@ -34999,19 +34993,19 @@
         <v>43</v>
       </c>
       <c r="B450" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G450" t="s">
         <v>2338</v>
       </c>
-      <c r="G450" t="s">
+      <c r="H450" t="s">
         <v>2339</v>
-      </c>
-      <c r="H450" t="s">
-        <v>2340</v>
       </c>
       <c r="I450" t="s">
         <v>1896</v>
       </c>
       <c r="J450" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="K450">
         <v>2010</v>
@@ -35023,19 +35017,19 @@
         <v>43</v>
       </c>
       <c r="B451" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G451" t="s">
         <v>2342</v>
       </c>
-      <c r="G451" t="s">
+      <c r="H451" t="s">
         <v>2343</v>
-      </c>
-      <c r="H451" t="s">
-        <v>2344</v>
       </c>
       <c r="I451" t="s">
         <v>49</v>
       </c>
       <c r="J451" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="K451">
         <v>2013</v>
@@ -35047,19 +35041,19 @@
         <v>43</v>
       </c>
       <c r="B452" t="s">
+        <v>2345</v>
+      </c>
+      <c r="G452" t="s">
         <v>2346</v>
       </c>
-      <c r="G452" t="s">
+      <c r="H452" t="s">
         <v>2347</v>
-      </c>
-      <c r="H452" t="s">
-        <v>2348</v>
       </c>
       <c r="I452" t="s">
         <v>287</v>
       </c>
       <c r="J452" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="K452">
         <v>2008</v>
@@ -35071,19 +35065,19 @@
         <v>43</v>
       </c>
       <c r="B453" t="s">
+        <v>2349</v>
+      </c>
+      <c r="G453" t="s">
         <v>2350</v>
       </c>
-      <c r="G453" t="s">
+      <c r="H453" t="s">
         <v>2351</v>
-      </c>
-      <c r="H453" t="s">
-        <v>2352</v>
       </c>
       <c r="I453" t="s">
         <v>677</v>
       </c>
       <c r="J453" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="K453">
         <v>2007</v>
@@ -35095,19 +35089,19 @@
         <v>43</v>
       </c>
       <c r="B454" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G454" t="s">
         <v>2354</v>
       </c>
-      <c r="G454" t="s">
+      <c r="H454" t="s">
         <v>2355</v>
       </c>
-      <c r="H454" t="s">
+      <c r="I454" t="s">
         <v>2356</v>
       </c>
-      <c r="I454" t="s">
+      <c r="J454" t="s">
         <v>2357</v>
-      </c>
-      <c r="J454" t="s">
-        <v>2358</v>
       </c>
       <c r="K454">
         <v>2003</v>
@@ -35119,19 +35113,19 @@
         <v>43</v>
       </c>
       <c r="B455" t="s">
+        <v>2358</v>
+      </c>
+      <c r="G455" t="s">
         <v>2359</v>
       </c>
-      <c r="G455" t="s">
+      <c r="H455" t="s">
         <v>2360</v>
-      </c>
-      <c r="H455" t="s">
-        <v>2361</v>
       </c>
       <c r="I455" t="s">
         <v>2159</v>
       </c>
       <c r="J455" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="K455">
         <v>2024</v>
@@ -35143,19 +35137,19 @@
         <v>43</v>
       </c>
       <c r="B456" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G456" t="s">
         <v>2363</v>
       </c>
-      <c r="G456" t="s">
+      <c r="H456" t="s">
         <v>2364</v>
       </c>
-      <c r="H456" t="s">
+      <c r="I456" t="s">
         <v>2365</v>
       </c>
-      <c r="I456" t="s">
+      <c r="J456" t="s">
         <v>2366</v>
-      </c>
-      <c r="J456" t="s">
-        <v>2367</v>
       </c>
       <c r="K456">
         <v>2022</v>
@@ -35167,19 +35161,19 @@
         <v>43</v>
       </c>
       <c r="B457" t="s">
+        <v>2367</v>
+      </c>
+      <c r="G457" t="s">
         <v>2368</v>
       </c>
-      <c r="G457" t="s">
+      <c r="H457" t="s">
         <v>2369</v>
-      </c>
-      <c r="H457" t="s">
-        <v>2370</v>
       </c>
       <c r="I457" t="s">
         <v>213</v>
       </c>
       <c r="J457" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="K457">
         <v>2019</v>
@@ -35191,19 +35185,19 @@
         <v>43</v>
       </c>
       <c r="B458" t="s">
+        <v>2371</v>
+      </c>
+      <c r="G458" t="s">
         <v>2372</v>
       </c>
-      <c r="G458" t="s">
+      <c r="H458" t="s">
         <v>2373</v>
       </c>
-      <c r="H458" t="s">
+      <c r="I458" t="s">
         <v>2374</v>
       </c>
-      <c r="I458" t="s">
+      <c r="J458" t="s">
         <v>2375</v>
-      </c>
-      <c r="J458" t="s">
-        <v>2376</v>
       </c>
       <c r="K458">
         <v>2024</v>
@@ -35215,19 +35209,19 @@
         <v>43</v>
       </c>
       <c r="B459" t="s">
+        <v>2376</v>
+      </c>
+      <c r="G459" t="s">
         <v>2377</v>
       </c>
-      <c r="G459" t="s">
+      <c r="H459" t="s">
         <v>2378</v>
-      </c>
-      <c r="H459" t="s">
-        <v>2379</v>
       </c>
       <c r="I459" t="s">
         <v>895</v>
       </c>
       <c r="J459" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="K459">
         <v>2003</v>
@@ -35239,19 +35233,19 @@
         <v>43</v>
       </c>
       <c r="B460" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G460" t="s">
         <v>2381</v>
       </c>
-      <c r="G460" t="s">
+      <c r="H460" t="s">
         <v>2382</v>
       </c>
-      <c r="H460" t="s">
+      <c r="I460" t="s">
         <v>2383</v>
       </c>
-      <c r="I460" t="s">
+      <c r="J460" t="s">
         <v>2384</v>
-      </c>
-      <c r="J460" t="s">
-        <v>2385</v>
       </c>
       <c r="K460">
         <v>2024</v>
@@ -35263,19 +35257,19 @@
         <v>43</v>
       </c>
       <c r="B461" t="s">
+        <v>2385</v>
+      </c>
+      <c r="G461" t="s">
         <v>2386</v>
       </c>
-      <c r="G461" t="s">
+      <c r="H461" t="s">
         <v>2387</v>
-      </c>
-      <c r="H461" t="s">
-        <v>2388</v>
       </c>
       <c r="I461" t="s">
         <v>49</v>
       </c>
       <c r="J461" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="K461">
         <v>2023</v>
@@ -35287,19 +35281,19 @@
         <v>43</v>
       </c>
       <c r="B462" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G462" t="s">
         <v>2390</v>
       </c>
-      <c r="G462" t="s">
+      <c r="H462" t="s">
         <v>2391</v>
       </c>
-      <c r="H462" t="s">
+      <c r="I462" t="s">
         <v>2392</v>
       </c>
-      <c r="I462" t="s">
+      <c r="J462" t="s">
         <v>2393</v>
-      </c>
-      <c r="J462" t="s">
-        <v>2394</v>
       </c>
       <c r="K462">
         <v>1995</v>
@@ -35311,19 +35305,19 @@
         <v>43</v>
       </c>
       <c r="B463" t="s">
+        <v>2394</v>
+      </c>
+      <c r="G463" t="s">
         <v>2395</v>
       </c>
-      <c r="G463" t="s">
+      <c r="H463" t="s">
         <v>2396</v>
-      </c>
-      <c r="H463" t="s">
-        <v>2397</v>
       </c>
       <c r="I463" t="s">
         <v>49</v>
       </c>
       <c r="J463" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="K463">
         <v>1989</v>
@@ -35335,19 +35329,19 @@
         <v>43</v>
       </c>
       <c r="B464" t="s">
+        <v>2397</v>
+      </c>
+      <c r="G464" t="s">
         <v>2398</v>
       </c>
-      <c r="G464" t="s">
+      <c r="H464" t="s">
         <v>2399</v>
-      </c>
-      <c r="H464" t="s">
-        <v>2400</v>
       </c>
       <c r="I464" t="s">
         <v>2227</v>
       </c>
       <c r="J464" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="K464">
         <v>1996</v>
@@ -35359,19 +35353,19 @@
         <v>43</v>
       </c>
       <c r="B465" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G465" t="s">
         <v>2402</v>
       </c>
-      <c r="G465" t="s">
+      <c r="H465" t="s">
         <v>2403</v>
       </c>
-      <c r="H465" t="s">
+      <c r="I465" t="s">
         <v>2404</v>
       </c>
-      <c r="I465" t="s">
+      <c r="J465" t="s">
         <v>2405</v>
-      </c>
-      <c r="J465" t="s">
-        <v>2406</v>
       </c>
       <c r="K465">
         <v>2021</v>
@@ -35383,19 +35377,19 @@
         <v>43</v>
       </c>
       <c r="B466" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G466" t="s">
         <v>2407</v>
       </c>
-      <c r="G466" t="s">
+      <c r="H466" t="s">
         <v>2408</v>
-      </c>
-      <c r="H466" t="s">
-        <v>2409</v>
       </c>
       <c r="I466" t="s">
         <v>123</v>
       </c>
       <c r="J466" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="K466">
         <v>2017</v>
@@ -35407,19 +35401,19 @@
         <v>43</v>
       </c>
       <c r="B467" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G467" t="s">
         <v>2411</v>
       </c>
-      <c r="G467" t="s">
+      <c r="H467" t="s">
         <v>2412</v>
       </c>
-      <c r="H467" t="s">
+      <c r="I467" t="s">
         <v>2413</v>
       </c>
-      <c r="I467" t="s">
+      <c r="J467" t="s">
         <v>2414</v>
-      </c>
-      <c r="J467" t="s">
-        <v>2415</v>
       </c>
       <c r="K467">
         <v>2023</v>
@@ -35431,19 +35425,19 @@
         <v>43</v>
       </c>
       <c r="B468" t="s">
+        <v>2415</v>
+      </c>
+      <c r="G468" t="s">
         <v>2416</v>
       </c>
-      <c r="G468" t="s">
+      <c r="H468" t="s">
         <v>2417</v>
       </c>
-      <c r="H468" t="s">
+      <c r="I468" t="s">
         <v>2418</v>
       </c>
-      <c r="I468" t="s">
+      <c r="J468" t="s">
         <v>2419</v>
-      </c>
-      <c r="J468" t="s">
-        <v>2420</v>
       </c>
       <c r="K468">
         <v>2012</v>
@@ -35455,19 +35449,19 @@
         <v>43</v>
       </c>
       <c r="B469" t="s">
+        <v>2420</v>
+      </c>
+      <c r="G469" t="s">
         <v>2421</v>
       </c>
-      <c r="G469" t="s">
+      <c r="H469" t="s">
         <v>2422</v>
       </c>
-      <c r="H469" t="s">
+      <c r="I469" t="s">
         <v>2423</v>
       </c>
-      <c r="I469" t="s">
+      <c r="J469" t="s">
         <v>2424</v>
-      </c>
-      <c r="J469" t="s">
-        <v>2425</v>
       </c>
       <c r="K469">
         <v>2021</v>
@@ -35479,19 +35473,19 @@
         <v>43</v>
       </c>
       <c r="B470" t="s">
+        <v>2425</v>
+      </c>
+      <c r="G470" t="s">
         <v>2426</v>
       </c>
-      <c r="G470" t="s">
+      <c r="H470" t="s">
         <v>2427</v>
-      </c>
-      <c r="H470" t="s">
-        <v>2428</v>
       </c>
       <c r="I470" t="s">
         <v>399</v>
       </c>
       <c r="J470" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="K470">
         <v>2022</v>
@@ -35503,19 +35497,19 @@
         <v>43</v>
       </c>
       <c r="B471" t="s">
+        <v>2429</v>
+      </c>
+      <c r="G471" t="s">
         <v>2430</v>
       </c>
-      <c r="G471" t="s">
+      <c r="H471" t="s">
         <v>2431</v>
-      </c>
-      <c r="H471" t="s">
-        <v>2432</v>
       </c>
       <c r="I471" t="s">
         <v>49</v>
       </c>
       <c r="J471" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="K471">
         <v>2018</v>
@@ -35527,19 +35521,19 @@
         <v>43</v>
       </c>
       <c r="B472" t="s">
+        <v>2433</v>
+      </c>
+      <c r="G472" t="s">
         <v>2434</v>
       </c>
-      <c r="G472" t="s">
+      <c r="H472" t="s">
         <v>2435</v>
-      </c>
-      <c r="H472" t="s">
-        <v>2436</v>
       </c>
       <c r="I472" t="s">
         <v>49</v>
       </c>
       <c r="J472" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="K472">
         <v>2021</v>
@@ -35551,19 +35545,19 @@
         <v>43</v>
       </c>
       <c r="B473" t="s">
+        <v>2437</v>
+      </c>
+      <c r="G473" t="s">
         <v>2438</v>
       </c>
-      <c r="G473" t="s">
+      <c r="H473" t="s">
         <v>2439</v>
-      </c>
-      <c r="H473" t="s">
-        <v>2440</v>
       </c>
       <c r="I473" t="s">
         <v>2227</v>
       </c>
       <c r="J473" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="K473">
         <v>1982</v>
@@ -35575,19 +35569,19 @@
         <v>43</v>
       </c>
       <c r="B474" t="s">
+        <v>2441</v>
+      </c>
+      <c r="G474" t="s">
         <v>2442</v>
       </c>
-      <c r="G474" t="s">
+      <c r="H474" t="s">
         <v>2443</v>
-      </c>
-      <c r="H474" t="s">
-        <v>2444</v>
       </c>
       <c r="I474" t="s">
         <v>2030</v>
       </c>
       <c r="J474" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="K474">
         <v>2014</v>
@@ -35599,19 +35593,19 @@
         <v>43</v>
       </c>
       <c r="B475" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G475" t="s">
         <v>2446</v>
       </c>
-      <c r="G475" t="s">
+      <c r="H475" t="s">
         <v>2447</v>
       </c>
-      <c r="H475" t="s">
+      <c r="I475" t="s">
         <v>2448</v>
       </c>
-      <c r="I475" t="s">
+      <c r="J475" t="s">
         <v>2449</v>
-      </c>
-      <c r="J475" t="s">
-        <v>2450</v>
       </c>
       <c r="K475">
         <v>2005</v>
@@ -35623,19 +35617,19 @@
         <v>43</v>
       </c>
       <c r="B476" t="s">
+        <v>2450</v>
+      </c>
+      <c r="G476" t="s">
         <v>2451</v>
       </c>
-      <c r="G476" t="s">
+      <c r="H476" t="s">
         <v>2452</v>
-      </c>
-      <c r="H476" t="s">
-        <v>2453</v>
       </c>
       <c r="I476" t="s">
         <v>1626</v>
       </c>
       <c r="J476" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="K476">
         <v>2011</v>
@@ -35647,19 +35641,19 @@
         <v>43</v>
       </c>
       <c r="B477" t="s">
+        <v>2454</v>
+      </c>
+      <c r="G477" t="s">
         <v>2455</v>
       </c>
-      <c r="G477" t="s">
+      <c r="H477" t="s">
         <v>2456</v>
-      </c>
-      <c r="H477" t="s">
-        <v>2457</v>
       </c>
       <c r="I477" t="s">
         <v>299</v>
       </c>
       <c r="J477" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="K477">
         <v>1979</v>
@@ -35671,19 +35665,19 @@
         <v>43</v>
       </c>
       <c r="B478" t="s">
+        <v>2458</v>
+      </c>
+      <c r="G478" t="s">
         <v>2459</v>
       </c>
-      <c r="G478" t="s">
+      <c r="H478" t="s">
         <v>2460</v>
-      </c>
-      <c r="H478" t="s">
-        <v>2461</v>
       </c>
       <c r="I478" t="s">
         <v>1289</v>
       </c>
       <c r="J478" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="K478">
         <v>1985</v>
@@ -35695,19 +35689,19 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
+        <v>2462</v>
+      </c>
+      <c r="G479" t="s">
         <v>2463</v>
       </c>
-      <c r="G479" t="s">
+      <c r="H479" t="s">
         <v>2464</v>
-      </c>
-      <c r="H479" t="s">
-        <v>2465</v>
       </c>
       <c r="I479" t="s">
         <v>1831</v>
       </c>
       <c r="J479" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="K479">
         <v>2011</v>
@@ -35719,19 +35713,19 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
+        <v>2466</v>
+      </c>
+      <c r="G480" t="s">
         <v>2467</v>
       </c>
-      <c r="G480" t="s">
+      <c r="H480" t="s">
         <v>2468</v>
-      </c>
-      <c r="H480" t="s">
-        <v>2469</v>
       </c>
       <c r="I480" t="s">
         <v>77</v>
       </c>
       <c r="J480" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="K480">
         <v>1976</v>
@@ -35743,19 +35737,19 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
+        <v>2470</v>
+      </c>
+      <c r="G481" t="s">
         <v>2471</v>
       </c>
-      <c r="G481" t="s">
+      <c r="H481" t="s">
         <v>2472</v>
-      </c>
-      <c r="H481" t="s">
-        <v>2473</v>
       </c>
       <c r="I481" t="s">
         <v>709</v>
       </c>
       <c r="J481" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="K481">
         <v>2006</v>
@@ -35767,19 +35761,19 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
+        <v>2474</v>
+      </c>
+      <c r="G482" t="s">
         <v>2475</v>
       </c>
-      <c r="G482" t="s">
+      <c r="H482" t="s">
         <v>2476</v>
-      </c>
-      <c r="H482" t="s">
-        <v>2477</v>
       </c>
       <c r="I482" t="s">
         <v>2159</v>
       </c>
       <c r="J482" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K482">
         <v>2001</v>
@@ -35791,19 +35785,19 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
+        <v>2478</v>
+      </c>
+      <c r="G483" t="s">
         <v>2479</v>
       </c>
-      <c r="G483" t="s">
+      <c r="H483" t="s">
         <v>2480</v>
-      </c>
-      <c r="H483" t="s">
-        <v>2481</v>
       </c>
       <c r="I483" t="s">
         <v>49</v>
       </c>
       <c r="J483" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="K483">
         <v>2020</v>
@@ -35815,19 +35809,19 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G484" t="s">
         <v>2483</v>
       </c>
-      <c r="G484" t="s">
+      <c r="H484" t="s">
         <v>2484</v>
-      </c>
-      <c r="H484" t="s">
-        <v>2485</v>
       </c>
       <c r="I484" t="s">
         <v>1334</v>
       </c>
       <c r="J484" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="K484">
         <v>2013</v>
@@ -35839,19 +35833,19 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G485" t="s">
         <v>2487</v>
       </c>
-      <c r="G485" t="s">
+      <c r="H485" t="s">
         <v>2488</v>
-      </c>
-      <c r="H485" t="s">
-        <v>2489</v>
       </c>
       <c r="I485" t="s">
         <v>287</v>
       </c>
       <c r="J485" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="K485">
         <v>2012</v>
@@ -35863,19 +35857,19 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G486" t="s">
         <v>2491</v>
       </c>
-      <c r="G486" t="s">
+      <c r="H486" t="s">
         <v>2492</v>
       </c>
-      <c r="H486" t="s">
+      <c r="I486" t="s">
         <v>2493</v>
       </c>
-      <c r="I486" t="s">
+      <c r="J486" t="s">
         <v>2494</v>
-      </c>
-      <c r="J486" t="s">
-        <v>2495</v>
       </c>
       <c r="K486">
         <v>1996</v>
@@ -35887,19 +35881,19 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
+        <v>2495</v>
+      </c>
+      <c r="G487" t="s">
         <v>2496</v>
       </c>
-      <c r="G487" t="s">
+      <c r="H487" t="s">
         <v>2497</v>
       </c>
-      <c r="H487" t="s">
+      <c r="I487" t="s">
         <v>2498</v>
       </c>
-      <c r="I487" t="s">
+      <c r="J487" t="s">
         <v>2499</v>
-      </c>
-      <c r="J487" t="s">
-        <v>2500</v>
       </c>
       <c r="K487">
         <v>1995</v>
@@ -35911,19 +35905,19 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
+        <v>2500</v>
+      </c>
+      <c r="G488" t="s">
         <v>2501</v>
       </c>
-      <c r="G488" t="s">
+      <c r="H488" t="s">
         <v>2502</v>
-      </c>
-      <c r="H488" t="s">
-        <v>2503</v>
       </c>
       <c r="I488" t="s">
         <v>49</v>
       </c>
       <c r="J488" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="K488">
         <v>2002</v>
@@ -35935,19 +35929,19 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G489" t="s">
         <v>2505</v>
       </c>
-      <c r="G489" t="s">
+      <c r="H489" t="s">
         <v>2506</v>
       </c>
-      <c r="H489" t="s">
+      <c r="I489" t="s">
         <v>2507</v>
       </c>
-      <c r="I489" t="s">
+      <c r="J489" t="s">
         <v>2508</v>
-      </c>
-      <c r="J489" t="s">
-        <v>2509</v>
       </c>
       <c r="K489">
         <v>2023</v>
@@ -35959,19 +35953,19 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
+        <v>2509</v>
+      </c>
+      <c r="G490" t="s">
         <v>2510</v>
       </c>
-      <c r="G490" t="s">
+      <c r="H490" t="s">
         <v>2511</v>
       </c>
-      <c r="H490" t="s">
+      <c r="I490" t="s">
         <v>2512</v>
       </c>
-      <c r="I490" t="s">
+      <c r="J490" t="s">
         <v>2513</v>
-      </c>
-      <c r="J490" t="s">
-        <v>2514</v>
       </c>
       <c r="K490">
         <v>2011</v>
@@ -35983,19 +35977,19 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
+        <v>2514</v>
+      </c>
+      <c r="G491" t="s">
         <v>2515</v>
       </c>
-      <c r="G491" t="s">
+      <c r="H491" t="s">
         <v>2516</v>
       </c>
-      <c r="H491" t="s">
+      <c r="I491" t="s">
         <v>2517</v>
       </c>
-      <c r="I491" t="s">
-        <v>2518</v>
-      </c>
       <c r="J491" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K491">
         <v>2011</v>
@@ -36007,19 +36001,19 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
+        <v>2518</v>
+      </c>
+      <c r="G492" t="s">
         <v>2519</v>
       </c>
-      <c r="G492" t="s">
+      <c r="H492" t="s">
         <v>2520</v>
-      </c>
-      <c r="H492" t="s">
-        <v>2521</v>
       </c>
       <c r="I492" t="s">
         <v>49</v>
       </c>
       <c r="J492" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="K492">
         <v>1984</v>
@@ -36031,19 +36025,19 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
+        <v>2522</v>
+      </c>
+      <c r="G493" t="s">
         <v>2523</v>
       </c>
-      <c r="G493" t="s">
+      <c r="H493" t="s">
         <v>2524</v>
       </c>
-      <c r="H493" t="s">
+      <c r="I493" t="s">
         <v>2525</v>
       </c>
-      <c r="I493" t="s">
+      <c r="J493" t="s">
         <v>2526</v>
-      </c>
-      <c r="J493" t="s">
-        <v>2527</v>
       </c>
       <c r="K493">
         <v>2017</v>
@@ -36055,19 +36049,19 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
+        <v>2527</v>
+      </c>
+      <c r="G494" t="s">
         <v>2528</v>
       </c>
-      <c r="G494" t="s">
+      <c r="H494" t="s">
         <v>2529</v>
-      </c>
-      <c r="H494" t="s">
-        <v>2530</v>
       </c>
       <c r="I494" t="s">
         <v>1702</v>
       </c>
       <c r="J494" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="K494">
         <v>2025</v>
@@ -36079,19 +36073,19 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
+        <v>2531</v>
+      </c>
+      <c r="G495" t="s">
         <v>2532</v>
       </c>
-      <c r="G495" t="s">
+      <c r="H495" t="s">
         <v>2533</v>
-      </c>
-      <c r="H495" t="s">
-        <v>2534</v>
       </c>
       <c r="I495" t="s">
         <v>628</v>
       </c>
       <c r="J495" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="K495">
         <v>2025</v>
@@ -36103,19 +36097,19 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
+        <v>2535</v>
+      </c>
+      <c r="G496" t="s">
+        <v>2519</v>
+      </c>
+      <c r="H496" t="s">
         <v>2536</v>
-      </c>
-      <c r="G496" t="s">
-        <v>2520</v>
-      </c>
-      <c r="H496" t="s">
-        <v>2537</v>
       </c>
       <c r="I496" t="s">
         <v>299</v>
       </c>
       <c r="J496" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="K496">
         <v>2020</v>
@@ -36127,19 +36121,19 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
+        <v>2538</v>
+      </c>
+      <c r="G497" t="s">
         <v>2539</v>
       </c>
-      <c r="G497" t="s">
+      <c r="H497" t="s">
         <v>2540</v>
       </c>
-      <c r="H497" t="s">
+      <c r="I497" t="s">
         <v>2541</v>
       </c>
-      <c r="I497" t="s">
+      <c r="J497" t="s">
         <v>2542</v>
-      </c>
-      <c r="J497" t="s">
-        <v>2543</v>
       </c>
       <c r="K497">
         <v>2019</v>
@@ -36151,19 +36145,19 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
+        <v>2543</v>
+      </c>
+      <c r="G498" t="s">
         <v>2544</v>
       </c>
-      <c r="G498" t="s">
+      <c r="H498" t="s">
         <v>2545</v>
       </c>
-      <c r="H498" t="s">
+      <c r="I498" t="s">
         <v>2546</v>
       </c>
-      <c r="I498" t="s">
+      <c r="J498" t="s">
         <v>2547</v>
-      </c>
-      <c r="J498" t="s">
-        <v>2548</v>
       </c>
       <c r="K498">
         <v>2023</v>
@@ -36175,19 +36169,19 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G499" t="s">
         <v>2549</v>
       </c>
-      <c r="G499" t="s">
+      <c r="H499" t="s">
         <v>2550</v>
-      </c>
-      <c r="H499" t="s">
-        <v>2551</v>
       </c>
       <c r="I499" t="s">
         <v>671</v>
       </c>
       <c r="J499" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="K499">
         <v>2001</v>
@@ -36199,19 +36193,19 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G500" t="s">
         <v>2553</v>
       </c>
-      <c r="G500" t="s">
+      <c r="H500" t="s">
         <v>2554</v>
-      </c>
-      <c r="H500" t="s">
-        <v>2555</v>
       </c>
       <c r="I500" t="s">
         <v>709</v>
       </c>
       <c r="J500" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="K500">
         <v>2022</v>
@@ -36223,19 +36217,19 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G501" t="s">
         <v>2557</v>
       </c>
-      <c r="G501" t="s">
+      <c r="H501" t="s">
         <v>2558</v>
-      </c>
-      <c r="H501" t="s">
-        <v>2559</v>
       </c>
       <c r="I501" t="s">
         <v>245</v>
       </c>
       <c r="J501" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="K501">
         <v>2001</v>
@@ -36247,19 +36241,19 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G502" t="s">
         <v>2561</v>
       </c>
-      <c r="G502" t="s">
+      <c r="H502" t="s">
         <v>2562</v>
-      </c>
-      <c r="H502" t="s">
-        <v>2563</v>
       </c>
       <c r="I502" t="s">
         <v>299</v>
       </c>
       <c r="J502" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="K502">
         <v>1976</v>
@@ -36271,19 +36265,19 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
+        <v>2564</v>
+      </c>
+      <c r="G503" t="s">
         <v>2565</v>
       </c>
-      <c r="G503" t="s">
+      <c r="H503" t="s">
         <v>2566</v>
       </c>
-      <c r="H503" t="s">
+      <c r="I503" t="s">
         <v>2567</v>
       </c>
-      <c r="I503" t="s">
+      <c r="J503" t="s">
         <v>2568</v>
-      </c>
-      <c r="J503" t="s">
-        <v>2569</v>
       </c>
       <c r="K503">
         <v>1981</v>
@@ -36295,19 +36289,19 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G504" t="s">
         <v>2570</v>
       </c>
-      <c r="G504" t="s">
+      <c r="H504" t="s">
         <v>2571</v>
       </c>
-      <c r="H504" t="s">
+      <c r="I504" t="s">
         <v>2572</v>
       </c>
-      <c r="I504" t="s">
+      <c r="J504" t="s">
         <v>2573</v>
-      </c>
-      <c r="J504" t="s">
-        <v>2574</v>
       </c>
       <c r="K504">
         <v>2025</v>
@@ -36319,19 +36313,19 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G505" t="s">
         <v>2575</v>
       </c>
-      <c r="G505" t="s">
+      <c r="H505" t="s">
         <v>2576</v>
       </c>
-      <c r="H505" t="s">
+      <c r="I505" t="s">
         <v>2577</v>
       </c>
-      <c r="I505" t="s">
+      <c r="J505" t="s">
         <v>2578</v>
-      </c>
-      <c r="J505" t="s">
-        <v>2579</v>
       </c>
       <c r="K505">
         <v>1998</v>
@@ -36343,19 +36337,19 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
+        <v>2579</v>
+      </c>
+      <c r="G506" t="s">
         <v>2580</v>
       </c>
-      <c r="G506" t="s">
+      <c r="H506" t="s">
         <v>2581</v>
-      </c>
-      <c r="H506" t="s">
-        <v>2582</v>
       </c>
       <c r="I506" t="s">
         <v>342</v>
       </c>
       <c r="J506" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="K506">
         <v>2010</v>
@@ -36367,19 +36361,19 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
+        <v>2583</v>
+      </c>
+      <c r="G507" t="s">
         <v>2584</v>
       </c>
-      <c r="G507" t="s">
+      <c r="H507" t="s">
         <v>2585</v>
-      </c>
-      <c r="H507" t="s">
-        <v>2586</v>
       </c>
       <c r="I507" t="s">
         <v>1993</v>
       </c>
       <c r="J507" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="K507">
         <v>2016</v>
@@ -36391,19 +36385,19 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
+        <v>2587</v>
+      </c>
+      <c r="G508" t="s">
         <v>2588</v>
       </c>
-      <c r="G508" t="s">
+      <c r="H508" t="s">
         <v>2589</v>
       </c>
-      <c r="H508" t="s">
+      <c r="I508" t="s">
         <v>2590</v>
       </c>
-      <c r="I508" t="s">
+      <c r="J508" t="s">
         <v>2591</v>
-      </c>
-      <c r="J508" t="s">
-        <v>2592</v>
       </c>
       <c r="K508">
         <v>2004</v>
@@ -36415,19 +36409,19 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
+        <v>2592</v>
+      </c>
+      <c r="G509" t="s">
         <v>2593</v>
       </c>
-      <c r="G509" t="s">
+      <c r="H509" t="s">
         <v>2594</v>
-      </c>
-      <c r="H509" t="s">
-        <v>2595</v>
       </c>
       <c r="I509" t="s">
         <v>469</v>
       </c>
       <c r="J509" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="K509">
         <v>1989</v>
@@ -36439,19 +36433,19 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G510" t="s">
         <v>2597</v>
       </c>
-      <c r="G510" t="s">
+      <c r="H510" t="s">
         <v>2598</v>
       </c>
-      <c r="H510" t="s">
+      <c r="I510" t="s">
         <v>2599</v>
       </c>
-      <c r="I510" t="s">
+      <c r="J510" t="s">
         <v>2600</v>
-      </c>
-      <c r="J510" t="s">
-        <v>2601</v>
       </c>
       <c r="K510">
         <v>2005</v>
@@ -36463,19 +36457,19 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
+        <v>2601</v>
+      </c>
+      <c r="G511" t="s">
         <v>2602</v>
       </c>
-      <c r="G511" t="s">
+      <c r="H511" t="s">
         <v>2603</v>
-      </c>
-      <c r="H511" t="s">
-        <v>2604</v>
       </c>
       <c r="I511" t="s">
         <v>393</v>
       </c>
       <c r="J511" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="K511">
         <v>2025</v>
@@ -36487,19 +36481,19 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
+        <v>2605</v>
+      </c>
+      <c r="G512" t="s">
         <v>2606</v>
       </c>
-      <c r="G512" t="s">
+      <c r="H512" t="s">
         <v>2607</v>
-      </c>
-      <c r="H512" t="s">
-        <v>2608</v>
       </c>
       <c r="I512" t="s">
         <v>1626</v>
       </c>
       <c r="J512" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="K512">
         <v>2018</v>
@@ -36511,19 +36505,19 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
+        <v>2609</v>
+      </c>
+      <c r="G513" t="s">
         <v>2610</v>
       </c>
-      <c r="G513" t="s">
+      <c r="H513" t="s">
         <v>2611</v>
-      </c>
-      <c r="H513" t="s">
-        <v>2612</v>
       </c>
       <c r="I513" t="s">
         <v>1474</v>
       </c>
       <c r="J513" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="K513">
         <v>2011</v>
@@ -36535,19 +36529,19 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G514" t="s">
         <v>2614</v>
       </c>
-      <c r="G514" t="s">
+      <c r="H514" t="s">
         <v>2615</v>
-      </c>
-      <c r="H514" t="s">
-        <v>2616</v>
       </c>
       <c r="I514" t="s">
         <v>1218</v>
       </c>
       <c r="J514" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="K514">
         <v>2024</v>
@@ -36559,19 +36553,19 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
+        <v>2617</v>
+      </c>
+      <c r="G515" t="s">
         <v>2618</v>
       </c>
-      <c r="G515" t="s">
+      <c r="H515" t="s">
         <v>2619</v>
-      </c>
-      <c r="H515" t="s">
-        <v>2620</v>
       </c>
       <c r="I515" t="s">
         <v>1753</v>
       </c>
       <c r="J515" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="K515">
         <v>2023</v>
@@ -36583,19 +36577,19 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G516" t="s">
         <v>2622</v>
       </c>
-      <c r="G516" t="s">
+      <c r="H516" t="s">
         <v>2623</v>
       </c>
-      <c r="H516" t="s">
+      <c r="I516" t="s">
         <v>2624</v>
       </c>
-      <c r="I516" t="s">
+      <c r="J516" t="s">
         <v>2625</v>
-      </c>
-      <c r="J516" t="s">
-        <v>2626</v>
       </c>
       <c r="K516">
         <v>2010</v>
@@ -36607,19 +36601,19 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
+        <v>2626</v>
+      </c>
+      <c r="G517" t="s">
         <v>2627</v>
       </c>
-      <c r="G517" t="s">
+      <c r="H517" t="s">
         <v>2628</v>
       </c>
-      <c r="H517" t="s">
+      <c r="I517" t="s">
         <v>2629</v>
       </c>
-      <c r="I517" t="s">
+      <c r="J517" t="s">
         <v>2630</v>
-      </c>
-      <c r="J517" t="s">
-        <v>2631</v>
       </c>
       <c r="K517">
         <v>2019</v>
@@ -36631,19 +36625,19 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G518" t="s">
         <v>2632</v>
       </c>
-      <c r="G518" t="s">
+      <c r="H518" t="s">
         <v>2633</v>
-      </c>
-      <c r="H518" t="s">
-        <v>2634</v>
       </c>
       <c r="I518" t="s">
         <v>49</v>
       </c>
       <c r="J518" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="K518">
         <v>1986</v>
@@ -36655,19 +36649,19 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G519" t="s">
         <v>2636</v>
       </c>
-      <c r="G519" t="s">
+      <c r="H519" t="s">
         <v>2637</v>
       </c>
-      <c r="H519" t="s">
+      <c r="I519" t="s">
         <v>2638</v>
       </c>
-      <c r="I519" t="s">
+      <c r="J519" t="s">
         <v>2639</v>
-      </c>
-      <c r="J519" t="s">
-        <v>2640</v>
       </c>
       <c r="K519">
         <v>2018</v>
@@ -36679,19 +36673,19 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
+        <v>2640</v>
+      </c>
+      <c r="G520" t="s">
         <v>2641</v>
       </c>
-      <c r="G520" t="s">
+      <c r="H520" t="s">
         <v>2642</v>
       </c>
-      <c r="H520" t="s">
+      <c r="I520" t="s">
         <v>2643</v>
       </c>
-      <c r="I520" t="s">
+      <c r="J520" t="s">
         <v>2644</v>
-      </c>
-      <c r="J520" t="s">
-        <v>2645</v>
       </c>
       <c r="K520">
         <v>2006</v>
@@ -36703,19 +36697,19 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
+        <v>2645</v>
+      </c>
+      <c r="G521" t="s">
         <v>2646</v>
       </c>
-      <c r="G521" t="s">
+      <c r="H521" t="s">
         <v>2647</v>
       </c>
-      <c r="H521" t="s">
+      <c r="I521" t="s">
         <v>2648</v>
       </c>
-      <c r="I521" t="s">
+      <c r="J521" t="s">
         <v>2649</v>
-      </c>
-      <c r="J521" t="s">
-        <v>2650</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -36727,19 +36721,19 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G522" t="s">
         <v>2651</v>
       </c>
-      <c r="G522" t="s">
+      <c r="H522" t="s">
         <v>2652</v>
-      </c>
-      <c r="H522" t="s">
-        <v>2653</v>
       </c>
       <c r="I522" t="s">
         <v>1172</v>
       </c>
       <c r="J522" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -36751,19 +36745,19 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
+        <v>2654</v>
+      </c>
+      <c r="G523" t="s">
         <v>2655</v>
       </c>
-      <c r="G523" t="s">
+      <c r="H523" t="s">
         <v>2656</v>
       </c>
-      <c r="H523" t="s">
+      <c r="I523" t="s">
         <v>2657</v>
       </c>
-      <c r="I523" t="s">
+      <c r="J523" t="s">
         <v>2658</v>
-      </c>
-      <c r="J523" t="s">
-        <v>2659</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -36775,19 +36769,19 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G524" t="s">
         <v>2660</v>
       </c>
-      <c r="G524" t="s">
+      <c r="H524" t="s">
         <v>2661</v>
-      </c>
-      <c r="H524" t="s">
-        <v>2662</v>
       </c>
       <c r="I524" t="s">
         <v>1702</v>
       </c>
       <c r="J524" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -36799,19 +36793,19 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
+        <v>2663</v>
+      </c>
+      <c r="G525" t="s">
         <v>2664</v>
       </c>
-      <c r="G525" t="s">
+      <c r="H525" t="s">
         <v>2665</v>
       </c>
-      <c r="H525" t="s">
+      <c r="I525" t="s">
         <v>2666</v>
       </c>
-      <c r="I525" t="s">
+      <c r="J525" t="s">
         <v>2667</v>
-      </c>
-      <c r="J525" t="s">
-        <v>2668</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -36823,19 +36817,19 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
+        <v>2668</v>
+      </c>
+      <c r="G526" t="s">
         <v>2669</v>
       </c>
-      <c r="G526" t="s">
+      <c r="H526" t="s">
         <v>2670</v>
-      </c>
-      <c r="H526" t="s">
-        <v>2671</v>
       </c>
       <c r="I526" t="s">
         <v>321</v>
       </c>
       <c r="J526" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -36847,19 +36841,19 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
+        <v>2672</v>
+      </c>
+      <c r="G527" t="s">
         <v>2673</v>
       </c>
-      <c r="G527" t="s">
+      <c r="H527" t="s">
         <v>2674</v>
       </c>
-      <c r="H527" t="s">
+      <c r="I527" t="s">
         <v>2675</v>
       </c>
-      <c r="I527" t="s">
+      <c r="J527" t="s">
         <v>2676</v>
-      </c>
-      <c r="J527" t="s">
-        <v>2677</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -36871,19 +36865,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
+        <v>2677</v>
+      </c>
+      <c r="G528" t="s">
         <v>2678</v>
       </c>
-      <c r="G528" t="s">
+      <c r="H528" t="s">
         <v>2679</v>
-      </c>
-      <c r="H528" t="s">
-        <v>2680</v>
       </c>
       <c r="I528" t="s">
         <v>1369</v>
       </c>
       <c r="J528" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -36895,19 +36889,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
+        <v>2681</v>
+      </c>
+      <c r="G529" t="s">
         <v>2682</v>
       </c>
-      <c r="G529" t="s">
+      <c r="H529" t="s">
         <v>2683</v>
       </c>
-      <c r="H529" t="s">
+      <c r="I529" t="s">
         <v>2684</v>
       </c>
-      <c r="I529" t="s">
+      <c r="J529" t="s">
         <v>2685</v>
-      </c>
-      <c r="J529" t="s">
-        <v>2686</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -36919,19 +36913,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
+        <v>2686</v>
+      </c>
+      <c r="G530" t="s">
         <v>2687</v>
       </c>
-      <c r="G530" t="s">
+      <c r="H530" t="s">
         <v>2688</v>
       </c>
-      <c r="H530" t="s">
+      <c r="I530" t="s">
         <v>2689</v>
       </c>
-      <c r="I530" t="s">
+      <c r="J530" t="s">
         <v>2690</v>
-      </c>
-      <c r="J530" t="s">
-        <v>2691</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -36943,19 +36937,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
+        <v>2691</v>
+      </c>
+      <c r="G531" t="s">
         <v>2692</v>
       </c>
-      <c r="G531" t="s">
+      <c r="H531" t="s">
         <v>2693</v>
-      </c>
-      <c r="H531" t="s">
-        <v>2694</v>
       </c>
       <c r="I531" t="s">
         <v>534</v>
       </c>
       <c r="J531" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -36967,19 +36961,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
+        <v>2695</v>
+      </c>
+      <c r="G532" t="s">
         <v>2696</v>
       </c>
-      <c r="G532" t="s">
+      <c r="H532" t="s">
         <v>2697</v>
-      </c>
-      <c r="H532" t="s">
-        <v>2698</v>
       </c>
       <c r="I532" t="s">
         <v>94</v>
       </c>
       <c r="J532" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -36991,19 +36985,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
+        <v>2699</v>
+      </c>
+      <c r="G533" t="s">
         <v>2700</v>
       </c>
-      <c r="G533" t="s">
+      <c r="H533" t="s">
         <v>2701</v>
-      </c>
-      <c r="H533" t="s">
-        <v>2702</v>
       </c>
       <c r="I533" t="s">
         <v>148</v>
       </c>
       <c r="J533" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -37015,19 +37009,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
+        <v>2703</v>
+      </c>
+      <c r="G534" t="s">
         <v>2704</v>
       </c>
-      <c r="G534" t="s">
+      <c r="H534" t="s">
         <v>2705</v>
-      </c>
-      <c r="H534" t="s">
-        <v>2706</v>
       </c>
       <c r="I534" t="s">
         <v>671</v>
       </c>
       <c r="J534" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -37039,19 +37033,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
+        <v>2707</v>
+      </c>
+      <c r="G535" t="s">
         <v>2708</v>
       </c>
-      <c r="G535" t="s">
+      <c r="H535" t="s">
         <v>2709</v>
       </c>
-      <c r="H535" t="s">
+      <c r="I535" t="s">
         <v>2710</v>
       </c>
-      <c r="I535" t="s">
+      <c r="J535" t="s">
         <v>2711</v>
-      </c>
-      <c r="J535" t="s">
-        <v>2712</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -37063,19 +37057,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
+        <v>2712</v>
+      </c>
+      <c r="G536" t="s">
         <v>2713</v>
       </c>
-      <c r="G536" t="s">
+      <c r="H536" t="s">
         <v>2714</v>
-      </c>
-      <c r="H536" t="s">
-        <v>2715</v>
       </c>
       <c r="I536" t="s">
         <v>638</v>
       </c>
       <c r="J536" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -37087,19 +37081,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
+        <v>2716</v>
+      </c>
+      <c r="G537" t="s">
         <v>2717</v>
       </c>
-      <c r="G537" t="s">
+      <c r="H537" t="s">
         <v>2718</v>
-      </c>
-      <c r="H537" t="s">
-        <v>2719</v>
       </c>
       <c r="I537" t="s">
         <v>416</v>
       </c>
       <c r="J537" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -37111,19 +37105,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G538" t="s">
         <v>2721</v>
       </c>
-      <c r="G538" t="s">
+      <c r="H538" t="s">
         <v>2722</v>
       </c>
-      <c r="H538" t="s">
+      <c r="I538" t="s">
         <v>2723</v>
       </c>
-      <c r="I538" t="s">
+      <c r="J538" t="s">
         <v>2724</v>
-      </c>
-      <c r="J538" t="s">
-        <v>2725</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -37135,19 +37129,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
+        <v>2725</v>
+      </c>
+      <c r="G539" t="s">
         <v>2726</v>
       </c>
-      <c r="G539" t="s">
+      <c r="H539" t="s">
         <v>2727</v>
-      </c>
-      <c r="H539" t="s">
-        <v>2728</v>
       </c>
       <c r="I539" t="s">
         <v>348</v>
       </c>
       <c r="J539" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -37159,19 +37153,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
+        <v>2729</v>
+      </c>
+      <c r="G540" t="s">
         <v>2730</v>
       </c>
-      <c r="G540" t="s">
+      <c r="H540" t="s">
         <v>2731</v>
-      </c>
-      <c r="H540" t="s">
-        <v>2732</v>
       </c>
       <c r="I540" t="s">
         <v>49</v>
       </c>
       <c r="J540" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -37183,19 +37177,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
+        <v>2733</v>
+      </c>
+      <c r="G541" t="s">
         <v>2734</v>
       </c>
-      <c r="G541" t="s">
+      <c r="H541" t="s">
         <v>2735</v>
-      </c>
-      <c r="H541" t="s">
-        <v>2736</v>
       </c>
       <c r="I541" t="s">
         <v>299</v>
       </c>
       <c r="J541" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -37207,19 +37201,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
+        <v>2737</v>
+      </c>
+      <c r="G542" t="s">
         <v>2738</v>
       </c>
-      <c r="G542" t="s">
+      <c r="H542" t="s">
         <v>2739</v>
-      </c>
-      <c r="H542" t="s">
-        <v>2740</v>
       </c>
       <c r="I542" t="s">
         <v>230</v>
       </c>
       <c r="J542" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -37231,19 +37225,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G543" t="s">
         <v>2742</v>
       </c>
-      <c r="G543" t="s">
+      <c r="H543" t="s">
         <v>2743</v>
-      </c>
-      <c r="H543" t="s">
-        <v>2744</v>
       </c>
       <c r="I543" t="s">
         <v>337</v>
       </c>
       <c r="J543" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -37255,19 +37249,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
+        <v>2745</v>
+      </c>
+      <c r="G544" t="s">
         <v>2746</v>
       </c>
-      <c r="G544" t="s">
+      <c r="H544" t="s">
         <v>2747</v>
       </c>
-      <c r="H544" t="s">
+      <c r="I544" t="s">
         <v>2748</v>
       </c>
-      <c r="I544" t="s">
+      <c r="J544" t="s">
         <v>2749</v>
-      </c>
-      <c r="J544" t="s">
-        <v>2750</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -37279,19 +37273,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
+        <v>2750</v>
+      </c>
+      <c r="G545" t="s">
         <v>2751</v>
       </c>
-      <c r="G545" t="s">
+      <c r="H545" t="s">
         <v>2752</v>
-      </c>
-      <c r="H545" t="s">
-        <v>2753</v>
       </c>
       <c r="I545" t="s">
         <v>881</v>
       </c>
       <c r="J545" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -37303,19 +37297,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
+        <v>2754</v>
+      </c>
+      <c r="G546" t="s">
         <v>2755</v>
       </c>
-      <c r="G546" t="s">
+      <c r="H546" t="s">
         <v>2756</v>
       </c>
-      <c r="H546" t="s">
+      <c r="I546" t="s">
+        <v>2638</v>
+      </c>
+      <c r="J546" t="s">
         <v>2757</v>
-      </c>
-      <c r="I546" t="s">
-        <v>2639</v>
-      </c>
-      <c r="J546" t="s">
-        <v>2758</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -37327,19 +37321,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G547" t="s">
         <v>2759</v>
       </c>
-      <c r="G547" t="s">
+      <c r="H547" t="s">
         <v>2760</v>
-      </c>
-      <c r="H547" t="s">
-        <v>2761</v>
       </c>
       <c r="I547" t="s">
         <v>258</v>
       </c>
       <c r="J547" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -37351,19 +37345,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
+        <v>2762</v>
+      </c>
+      <c r="G548" t="s">
         <v>2763</v>
       </c>
-      <c r="G548" t="s">
+      <c r="H548" t="s">
         <v>2764</v>
-      </c>
-      <c r="H548" t="s">
-        <v>2765</v>
       </c>
       <c r="I548" t="s">
         <v>709</v>
       </c>
       <c r="J548" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -37375,19 +37369,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
+        <v>2766</v>
+      </c>
+      <c r="G549" t="s">
         <v>2767</v>
       </c>
-      <c r="G549" t="s">
+      <c r="H549" t="s">
         <v>2768</v>
-      </c>
-      <c r="H549" t="s">
-        <v>2769</v>
       </c>
       <c r="I549" t="s">
         <v>49</v>
       </c>
       <c r="J549" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -37399,19 +37393,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
+        <v>2770</v>
+      </c>
+      <c r="G550" t="s">
         <v>2771</v>
       </c>
-      <c r="G550" t="s">
+      <c r="H550" t="s">
         <v>2772</v>
-      </c>
-      <c r="H550" t="s">
-        <v>2773</v>
       </c>
       <c r="I550" t="s">
         <v>142</v>
       </c>
       <c r="J550" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -37423,19 +37417,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
+        <v>2774</v>
+      </c>
+      <c r="G551" t="s">
         <v>2775</v>
       </c>
-      <c r="G551" t="s">
+      <c r="H551" t="s">
         <v>2776</v>
       </c>
-      <c r="H551" t="s">
+      <c r="I551" t="s">
         <v>2777</v>
       </c>
-      <c r="I551" t="s">
+      <c r="J551" t="s">
         <v>2778</v>
-      </c>
-      <c r="J551" t="s">
-        <v>2779</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -37447,19 +37441,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
+        <v>2779</v>
+      </c>
+      <c r="G552" t="s">
         <v>2780</v>
       </c>
-      <c r="G552" t="s">
+      <c r="H552" t="s">
         <v>2781</v>
       </c>
-      <c r="H552" t="s">
+      <c r="I552" t="s">
         <v>2782</v>
       </c>
-      <c r="I552" t="s">
+      <c r="J552" t="s">
         <v>2783</v>
-      </c>
-      <c r="J552" t="s">
-        <v>2784</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -37471,19 +37465,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
+        <v>2784</v>
+      </c>
+      <c r="G553" t="s">
         <v>2785</v>
       </c>
-      <c r="G553" t="s">
+      <c r="H553" t="s">
         <v>2786</v>
       </c>
-      <c r="H553" t="s">
+      <c r="I553" t="s">
         <v>2787</v>
       </c>
-      <c r="I553" t="s">
+      <c r="J553" t="s">
         <v>2788</v>
-      </c>
-      <c r="J553" t="s">
-        <v>2789</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -37495,19 +37489,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
+        <v>2789</v>
+      </c>
+      <c r="G554" t="s">
         <v>2790</v>
       </c>
-      <c r="G554" t="s">
+      <c r="H554" t="s">
         <v>2791</v>
       </c>
-      <c r="H554" t="s">
+      <c r="I554" t="s">
         <v>2792</v>
       </c>
-      <c r="I554" t="s">
+      <c r="J554" t="s">
         <v>2793</v>
-      </c>
-      <c r="J554" t="s">
-        <v>2794</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -37519,19 +37513,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
+        <v>2794</v>
+      </c>
+      <c r="G555" t="s">
         <v>2795</v>
       </c>
-      <c r="G555" t="s">
+      <c r="H555" t="s">
         <v>2796</v>
-      </c>
-      <c r="H555" t="s">
-        <v>2797</v>
       </c>
       <c r="I555" t="s">
         <v>416</v>
       </c>
       <c r="J555" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -37543,19 +37537,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
+        <v>2798</v>
+      </c>
+      <c r="G556" t="s">
         <v>2799</v>
       </c>
-      <c r="G556" t="s">
+      <c r="H556" t="s">
         <v>2800</v>
       </c>
-      <c r="H556" t="s">
+      <c r="I556" t="s">
         <v>2801</v>
       </c>
-      <c r="I556" t="s">
+      <c r="J556" t="s">
         <v>2802</v>
-      </c>
-      <c r="J556" t="s">
-        <v>2803</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -37567,19 +37561,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
+        <v>2803</v>
+      </c>
+      <c r="G557" t="s">
         <v>2804</v>
       </c>
-      <c r="G557" t="s">
+      <c r="H557" t="s">
         <v>2805</v>
-      </c>
-      <c r="H557" t="s">
-        <v>2806</v>
       </c>
       <c r="I557" t="s">
         <v>348</v>
       </c>
       <c r="J557" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -37591,19 +37585,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
+        <v>2807</v>
+      </c>
+      <c r="G558" t="s">
         <v>2808</v>
       </c>
-      <c r="G558" t="s">
+      <c r="H558" t="s">
         <v>2809</v>
-      </c>
-      <c r="H558" t="s">
-        <v>2810</v>
       </c>
       <c r="I558" t="s">
         <v>230</v>
       </c>
       <c r="J558" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -37615,19 +37609,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G559" t="s">
         <v>2812</v>
       </c>
-      <c r="G559" t="s">
+      <c r="H559" t="s">
         <v>2813</v>
       </c>
-      <c r="H559" t="s">
+      <c r="I559" t="s">
         <v>2814</v>
       </c>
-      <c r="I559" t="s">
+      <c r="J559" t="s">
         <v>2815</v>
-      </c>
-      <c r="J559" t="s">
-        <v>2816</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -37639,19 +37633,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
+        <v>2816</v>
+      </c>
+      <c r="G560" t="s">
         <v>2817</v>
       </c>
-      <c r="G560" t="s">
+      <c r="H560" t="s">
         <v>2818</v>
-      </c>
-      <c r="H560" t="s">
-        <v>2819</v>
       </c>
       <c r="I560" t="s">
         <v>992</v>
       </c>
       <c r="J560" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -37663,19 +37657,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
+        <v>2820</v>
+      </c>
+      <c r="G561" t="s">
         <v>2821</v>
       </c>
-      <c r="G561" t="s">
+      <c r="H561" t="s">
         <v>2822</v>
-      </c>
-      <c r="H561" t="s">
-        <v>2823</v>
       </c>
       <c r="I561" t="s">
         <v>49</v>
       </c>
       <c r="J561" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -37687,19 +37681,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
+        <v>2824</v>
+      </c>
+      <c r="G562" t="s">
         <v>2825</v>
       </c>
-      <c r="G562" t="s">
+      <c r="H562" t="s">
         <v>2826</v>
-      </c>
-      <c r="H562" t="s">
-        <v>2827</v>
       </c>
       <c r="I562" t="s">
         <v>49</v>
       </c>
       <c r="J562" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -37711,19 +37705,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
+        <v>2828</v>
+      </c>
+      <c r="G563" t="s">
         <v>2829</v>
       </c>
-      <c r="G563" t="s">
+      <c r="H563" t="s">
         <v>2830</v>
-      </c>
-      <c r="H563" t="s">
-        <v>2831</v>
       </c>
       <c r="I563" t="s">
         <v>49</v>
       </c>
       <c r="J563" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -37735,19 +37729,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
+        <v>2832</v>
+      </c>
+      <c r="G564" t="s">
         <v>2833</v>
       </c>
-      <c r="G564" t="s">
+      <c r="H564" t="s">
         <v>2834</v>
-      </c>
-      <c r="H564" t="s">
-        <v>2835</v>
       </c>
       <c r="I564" t="s">
         <v>1436</v>
       </c>
       <c r="J564" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -37759,19 +37753,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
+        <v>2836</v>
+      </c>
+      <c r="G565" t="s">
         <v>2837</v>
       </c>
-      <c r="G565" t="s">
+      <c r="H565" t="s">
         <v>2838</v>
       </c>
-      <c r="H565" t="s">
+      <c r="I565" t="s">
         <v>2839</v>
       </c>
-      <c r="I565" t="s">
+      <c r="J565" t="s">
         <v>2840</v>
-      </c>
-      <c r="J565" t="s">
-        <v>2841</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -37783,19 +37777,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
+        <v>2841</v>
+      </c>
+      <c r="G566" t="s">
         <v>2842</v>
       </c>
-      <c r="G566" t="s">
+      <c r="H566" t="s">
         <v>2843</v>
-      </c>
-      <c r="H566" t="s">
-        <v>2844</v>
       </c>
       <c r="I566" t="s">
         <v>449</v>
       </c>
       <c r="J566" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -37807,19 +37801,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
+        <v>2845</v>
+      </c>
+      <c r="G567" t="s">
         <v>2846</v>
       </c>
-      <c r="G567" t="s">
+      <c r="H567" t="s">
         <v>2847</v>
-      </c>
-      <c r="H567" t="s">
-        <v>2848</v>
       </c>
       <c r="I567" t="s">
         <v>895</v>
       </c>
       <c r="J567" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -37831,19 +37825,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G568" t="s">
         <v>2850</v>
       </c>
-      <c r="G568" t="s">
+      <c r="H568" t="s">
         <v>2851</v>
       </c>
-      <c r="H568" t="s">
+      <c r="I568" t="s">
         <v>2852</v>
       </c>
-      <c r="I568" t="s">
+      <c r="J568" t="s">
         <v>2853</v>
-      </c>
-      <c r="J568" t="s">
-        <v>2854</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -37855,19 +37849,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
+        <v>2854</v>
+      </c>
+      <c r="G569" t="s">
         <v>2855</v>
       </c>
-      <c r="G569" t="s">
+      <c r="H569" t="s">
         <v>2856</v>
-      </c>
-      <c r="H569" t="s">
-        <v>2857</v>
       </c>
       <c r="I569" t="s">
         <v>49</v>
       </c>
       <c r="J569" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -37879,19 +37873,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G570" t="s">
         <v>2859</v>
       </c>
-      <c r="G570" t="s">
+      <c r="H570" t="s">
         <v>2860</v>
-      </c>
-      <c r="H570" t="s">
-        <v>2861</v>
       </c>
       <c r="I570" t="s">
         <v>49</v>
       </c>
       <c r="J570" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -37903,19 +37897,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
+        <v>2862</v>
+      </c>
+      <c r="G571" t="s">
         <v>2863</v>
       </c>
-      <c r="G571" t="s">
+      <c r="H571" t="s">
         <v>2864</v>
-      </c>
-      <c r="H571" t="s">
-        <v>2865</v>
       </c>
       <c r="I571" t="s">
         <v>957</v>
       </c>
       <c r="J571" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -37927,19 +37921,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
+        <v>2866</v>
+      </c>
+      <c r="G572" t="s">
         <v>2867</v>
       </c>
-      <c r="G572" t="s">
+      <c r="H572" t="s">
         <v>2868</v>
       </c>
-      <c r="H572" t="s">
+      <c r="I572" t="s">
         <v>2869</v>
       </c>
-      <c r="I572" t="s">
+      <c r="J572" t="s">
         <v>2870</v>
-      </c>
-      <c r="J572" t="s">
-        <v>2871</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -37951,19 +37945,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
+        <v>2871</v>
+      </c>
+      <c r="G573" t="s">
         <v>2872</v>
       </c>
-      <c r="G573" t="s">
+      <c r="H573" t="s">
         <v>2873</v>
-      </c>
-      <c r="H573" t="s">
-        <v>2874</v>
       </c>
       <c r="I573" t="s">
         <v>677</v>
       </c>
       <c r="J573" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -37975,19 +37969,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
+        <v>2875</v>
+      </c>
+      <c r="G574" t="s">
         <v>2876</v>
       </c>
-      <c r="G574" t="s">
+      <c r="H574" t="s">
         <v>2877</v>
-      </c>
-      <c r="H574" t="s">
-        <v>2878</v>
       </c>
       <c r="I574" t="s">
         <v>49</v>
       </c>
       <c r="J574" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -37999,19 +37993,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
+        <v>2879</v>
+      </c>
+      <c r="G575" t="s">
         <v>2880</v>
       </c>
-      <c r="G575" t="s">
+      <c r="H575" t="s">
         <v>2881</v>
       </c>
-      <c r="H575" t="s">
+      <c r="I575" t="s">
         <v>2882</v>
       </c>
-      <c r="I575" t="s">
+      <c r="J575" t="s">
         <v>2883</v>
-      </c>
-      <c r="J575" t="s">
-        <v>2884</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -38023,19 +38017,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
+        <v>2884</v>
+      </c>
+      <c r="G576" t="s">
         <v>2885</v>
       </c>
-      <c r="G576" t="s">
+      <c r="H576" t="s">
         <v>2886</v>
-      </c>
-      <c r="H576" t="s">
-        <v>2887</v>
       </c>
       <c r="I576" t="s">
         <v>709</v>
       </c>
       <c r="J576" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -38047,19 +38041,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
+        <v>2888</v>
+      </c>
+      <c r="G577" t="s">
         <v>2889</v>
       </c>
-      <c r="G577" t="s">
+      <c r="H577" t="s">
         <v>2890</v>
-      </c>
-      <c r="H577" t="s">
-        <v>2891</v>
       </c>
       <c r="I577" t="s">
         <v>895</v>
       </c>
       <c r="J577" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -38071,19 +38065,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
+        <v>2892</v>
+      </c>
+      <c r="G578" t="s">
         <v>2893</v>
       </c>
-      <c r="G578" t="s">
+      <c r="H578" t="s">
         <v>2894</v>
-      </c>
-      <c r="H578" t="s">
-        <v>2895</v>
       </c>
       <c r="I578" t="s">
         <v>709</v>
       </c>
       <c r="J578" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -38095,19 +38089,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
+        <v>2896</v>
+      </c>
+      <c r="G579" t="s">
         <v>2897</v>
       </c>
-      <c r="G579" t="s">
+      <c r="H579" t="s">
         <v>2898</v>
       </c>
-      <c r="H579" t="s">
+      <c r="I579" t="s">
         <v>2899</v>
       </c>
-      <c r="I579" t="s">
+      <c r="J579" t="s">
         <v>2900</v>
-      </c>
-      <c r="J579" t="s">
-        <v>2901</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -38119,19 +38113,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
+        <v>2901</v>
+      </c>
+      <c r="G580" t="s">
         <v>2902</v>
       </c>
-      <c r="G580" t="s">
+      <c r="H580" t="s">
         <v>2903</v>
-      </c>
-      <c r="H580" t="s">
-        <v>2904</v>
       </c>
       <c r="I580" t="s">
         <v>245</v>
       </c>
       <c r="J580" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -38143,19 +38137,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
+        <v>2905</v>
+      </c>
+      <c r="G581" t="s">
         <v>2906</v>
       </c>
-      <c r="G581" t="s">
+      <c r="H581" t="s">
         <v>2907</v>
-      </c>
-      <c r="H581" t="s">
-        <v>2908</v>
       </c>
       <c r="I581" t="s">
         <v>709</v>
       </c>
       <c r="J581" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -38167,19 +38161,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
+        <v>2908</v>
+      </c>
+      <c r="G582" t="s">
         <v>2909</v>
       </c>
-      <c r="G582" t="s">
+      <c r="H582" t="s">
         <v>2910</v>
-      </c>
-      <c r="H582" t="s">
-        <v>2911</v>
       </c>
       <c r="I582" t="s">
         <v>190</v>
       </c>
       <c r="J582" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -38191,19 +38185,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
+        <v>2912</v>
+      </c>
+      <c r="G583" t="s">
         <v>2913</v>
       </c>
-      <c r="G583" t="s">
+      <c r="H583" t="s">
         <v>2914</v>
-      </c>
-      <c r="H583" t="s">
-        <v>2915</v>
       </c>
       <c r="I583" t="s">
         <v>2159</v>
       </c>
       <c r="J583" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -38215,19 +38209,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
+        <v>2916</v>
+      </c>
+      <c r="G584" t="s">
         <v>2917</v>
       </c>
-      <c r="G584" t="s">
+      <c r="H584" t="s">
         <v>2918</v>
       </c>
-      <c r="H584" t="s">
+      <c r="I584" t="s">
         <v>2919</v>
       </c>
-      <c r="I584" t="s">
+      <c r="J584" t="s">
         <v>2920</v>
-      </c>
-      <c r="J584" t="s">
-        <v>2921</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -38239,19 +38233,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
+        <v>2921</v>
+      </c>
+      <c r="G585" t="s">
         <v>2922</v>
       </c>
-      <c r="G585" t="s">
+      <c r="H585" t="s">
         <v>2923</v>
-      </c>
-      <c r="H585" t="s">
-        <v>2924</v>
       </c>
       <c r="I585" t="s">
         <v>729</v>
       </c>
       <c r="J585" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -38263,19 +38257,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
+        <v>2925</v>
+      </c>
+      <c r="G586" t="s">
         <v>2926</v>
       </c>
-      <c r="G586" t="s">
+      <c r="H586" t="s">
         <v>2927</v>
-      </c>
-      <c r="H586" t="s">
-        <v>2928</v>
       </c>
       <c r="I586" t="s">
         <v>2244</v>
       </c>
       <c r="J586" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -38287,19 +38281,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
+        <v>2929</v>
+      </c>
+      <c r="G587" t="s">
         <v>2930</v>
       </c>
-      <c r="G587" t="s">
+      <c r="H587" t="s">
         <v>2931</v>
       </c>
-      <c r="H587" t="s">
+      <c r="I587" t="s">
         <v>2932</v>
       </c>
-      <c r="I587" t="s">
+      <c r="J587" t="s">
         <v>2933</v>
-      </c>
-      <c r="J587" t="s">
-        <v>2934</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -38311,19 +38305,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
+        <v>2934</v>
+      </c>
+      <c r="G588" t="s">
         <v>2935</v>
       </c>
-      <c r="G588" t="s">
+      <c r="H588" t="s">
         <v>2936</v>
-      </c>
-      <c r="H588" t="s">
-        <v>2937</v>
       </c>
       <c r="I588" t="s">
         <v>1334</v>
       </c>
       <c r="J588" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -38335,19 +38329,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
+        <v>2938</v>
+      </c>
+      <c r="G589" t="s">
         <v>2939</v>
       </c>
-      <c r="G589" t="s">
+      <c r="H589" t="s">
         <v>2940</v>
-      </c>
-      <c r="H589" t="s">
-        <v>2941</v>
       </c>
       <c r="I589" t="s">
         <v>957</v>
       </c>
       <c r="J589" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -38359,19 +38353,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
+        <v>2942</v>
+      </c>
+      <c r="G590" t="s">
         <v>2943</v>
       </c>
-      <c r="G590" t="s">
+      <c r="H590" t="s">
         <v>2944</v>
       </c>
-      <c r="H590" t="s">
+      <c r="I590" t="s">
         <v>2945</v>
       </c>
-      <c r="I590" t="s">
+      <c r="J590" t="s">
         <v>2946</v>
-      </c>
-      <c r="J590" t="s">
-        <v>2947</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -38383,19 +38377,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
+        <v>2947</v>
+      </c>
+      <c r="G591" t="s">
         <v>2948</v>
       </c>
-      <c r="G591" t="s">
+      <c r="H591" t="s">
         <v>2949</v>
       </c>
-      <c r="H591" t="s">
+      <c r="I591" t="s">
         <v>2950</v>
       </c>
-      <c r="I591" t="s">
+      <c r="J591" t="s">
         <v>2951</v>
-      </c>
-      <c r="J591" t="s">
-        <v>2952</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -38407,19 +38401,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
+        <v>2952</v>
+      </c>
+      <c r="G592" t="s">
         <v>2953</v>
       </c>
-      <c r="G592" t="s">
+      <c r="H592" t="s">
         <v>2954</v>
-      </c>
-      <c r="H592" t="s">
-        <v>2955</v>
       </c>
       <c r="I592" t="s">
         <v>2159</v>
       </c>
       <c r="J592" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -38431,19 +38425,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
+        <v>2956</v>
+      </c>
+      <c r="G593" t="s">
         <v>2957</v>
       </c>
-      <c r="G593" t="s">
+      <c r="H593" t="s">
         <v>2958</v>
-      </c>
-      <c r="H593" t="s">
-        <v>2959</v>
       </c>
       <c r="I593" t="s">
         <v>2019</v>
       </c>
       <c r="J593" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -38455,19 +38449,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
+        <v>2960</v>
+      </c>
+      <c r="G594" t="s">
         <v>2961</v>
       </c>
-      <c r="G594" t="s">
+      <c r="H594" t="s">
         <v>2962</v>
-      </c>
-      <c r="H594" t="s">
-        <v>2963</v>
       </c>
       <c r="I594" t="s">
         <v>968</v>
       </c>
       <c r="J594" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -38479,19 +38473,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
+        <v>2964</v>
+      </c>
+      <c r="G595" t="s">
         <v>2965</v>
       </c>
-      <c r="G595" t="s">
+      <c r="H595" t="s">
         <v>2966</v>
       </c>
-      <c r="H595" t="s">
+      <c r="I595" t="s">
         <v>2967</v>
       </c>
-      <c r="I595" t="s">
+      <c r="J595" t="s">
         <v>2968</v>
-      </c>
-      <c r="J595" t="s">
-        <v>2969</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -38503,19 +38497,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G596" t="s">
         <v>2970</v>
       </c>
-      <c r="G596" t="s">
+      <c r="H596" t="s">
         <v>2971</v>
       </c>
-      <c r="H596" t="s">
+      <c r="I596" t="s">
         <v>2972</v>
       </c>
-      <c r="I596" t="s">
+      <c r="J596" t="s">
         <v>2973</v>
-      </c>
-      <c r="J596" t="s">
-        <v>2974</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -38527,19 +38521,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
+        <v>2974</v>
+      </c>
+      <c r="G597" t="s">
         <v>2975</v>
       </c>
-      <c r="G597" t="s">
+      <c r="H597" t="s">
         <v>2976</v>
-      </c>
-      <c r="H597" t="s">
-        <v>2977</v>
       </c>
       <c r="I597" t="s">
         <v>49</v>
       </c>
       <c r="J597" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -38551,19 +38545,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
+        <v>2978</v>
+      </c>
+      <c r="G598" t="s">
         <v>2979</v>
       </c>
-      <c r="G598" t="s">
+      <c r="H598" t="s">
         <v>2980</v>
-      </c>
-      <c r="H598" t="s">
-        <v>2981</v>
       </c>
       <c r="I598" t="s">
         <v>1284</v>
       </c>
       <c r="J598" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -38575,19 +38569,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
+        <v>2982</v>
+      </c>
+      <c r="G599" t="s">
         <v>2983</v>
       </c>
-      <c r="G599" t="s">
+      <c r="H599" t="s">
         <v>2984</v>
-      </c>
-      <c r="H599" t="s">
-        <v>2985</v>
       </c>
       <c r="I599" t="s">
         <v>1626</v>
       </c>
       <c r="J599" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -38599,19 +38593,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
+        <v>2986</v>
+      </c>
+      <c r="G600" t="s">
         <v>2987</v>
       </c>
-      <c r="G600" t="s">
+      <c r="H600" t="s">
         <v>2988</v>
-      </c>
-      <c r="H600" t="s">
-        <v>2989</v>
       </c>
       <c r="I600" t="s">
         <v>49</v>
       </c>
       <c r="J600" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -38623,19 +38617,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
+        <v>2990</v>
+      </c>
+      <c r="G601" t="s">
         <v>2991</v>
       </c>
-      <c r="G601" t="s">
+      <c r="H601" t="s">
         <v>2992</v>
       </c>
-      <c r="H601" t="s">
+      <c r="I601" t="s">
+        <v>2950</v>
+      </c>
+      <c r="J601" t="s">
         <v>2993</v>
-      </c>
-      <c r="I601" t="s">
-        <v>2951</v>
-      </c>
-      <c r="J601" t="s">
-        <v>2994</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -38647,19 +38641,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
+        <v>2994</v>
+      </c>
+      <c r="G602" t="s">
         <v>2995</v>
       </c>
-      <c r="G602" t="s">
+      <c r="H602" t="s">
         <v>2996</v>
       </c>
-      <c r="H602" t="s">
+      <c r="I602" t="s">
+        <v>2839</v>
+      </c>
+      <c r="J602" t="s">
         <v>2997</v>
-      </c>
-      <c r="I602" t="s">
-        <v>2840</v>
-      </c>
-      <c r="J602" t="s">
-        <v>2998</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -38671,19 +38665,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
+        <v>2998</v>
+      </c>
+      <c r="G603" t="s">
         <v>2999</v>
       </c>
-      <c r="G603" t="s">
+      <c r="H603" t="s">
         <v>3000</v>
       </c>
-      <c r="H603" t="s">
+      <c r="I603" t="s">
         <v>3001</v>
       </c>
-      <c r="I603" t="s">
+      <c r="J603" t="s">
         <v>3002</v>
-      </c>
-      <c r="J603" t="s">
-        <v>3003</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -38695,19 +38689,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
+        <v>3003</v>
+      </c>
+      <c r="G604" t="s">
         <v>3004</v>
       </c>
-      <c r="G604" t="s">
+      <c r="H604" t="s">
         <v>3005</v>
-      </c>
-      <c r="H604" t="s">
-        <v>3006</v>
       </c>
       <c r="I604" t="s">
         <v>94</v>
       </c>
       <c r="J604" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -38719,19 +38713,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
+        <v>3007</v>
+      </c>
+      <c r="G605" t="s">
         <v>3008</v>
       </c>
-      <c r="G605" t="s">
+      <c r="H605" t="s">
         <v>3009</v>
-      </c>
-      <c r="H605" t="s">
-        <v>3010</v>
       </c>
       <c r="I605" t="s">
         <v>1896</v>
       </c>
       <c r="J605" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -38743,19 +38737,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
+        <v>3011</v>
+      </c>
+      <c r="G606" t="s">
         <v>3012</v>
       </c>
-      <c r="G606" t="s">
+      <c r="H606" t="s">
         <v>3013</v>
       </c>
-      <c r="H606" t="s">
+      <c r="I606" t="s">
         <v>3014</v>
       </c>
-      <c r="I606" t="s">
+      <c r="J606" t="s">
         <v>3015</v>
-      </c>
-      <c r="J606" t="s">
-        <v>3016</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -38767,19 +38761,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
+        <v>3016</v>
+      </c>
+      <c r="G607" t="s">
         <v>3017</v>
       </c>
-      <c r="G607" t="s">
+      <c r="H607" t="s">
         <v>3018</v>
-      </c>
-      <c r="H607" t="s">
-        <v>3019</v>
       </c>
       <c r="I607" t="s">
         <v>1495</v>
       </c>
       <c r="J607" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -38791,19 +38785,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
+        <v>3020</v>
+      </c>
+      <c r="G608" t="s">
         <v>3021</v>
       </c>
-      <c r="G608" t="s">
+      <c r="H608" t="s">
         <v>3022</v>
-      </c>
-      <c r="H608" t="s">
-        <v>3023</v>
       </c>
       <c r="I608" t="s">
         <v>1495</v>
       </c>
       <c r="J608" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -38815,19 +38809,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
+        <v>3024</v>
+      </c>
+      <c r="G609" t="s">
         <v>3025</v>
       </c>
-      <c r="G609" t="s">
+      <c r="H609" t="s">
         <v>3026</v>
       </c>
-      <c r="H609" t="s">
+      <c r="I609" t="s">
         <v>3027</v>
       </c>
-      <c r="I609" t="s">
+      <c r="J609" t="s">
         <v>3028</v>
-      </c>
-      <c r="J609" t="s">
-        <v>3029</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -38839,19 +38833,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
+        <v>3029</v>
+      </c>
+      <c r="G610" t="s">
         <v>3030</v>
       </c>
-      <c r="G610" t="s">
+      <c r="H610" t="s">
         <v>3031</v>
-      </c>
-      <c r="H610" t="s">
-        <v>3032</v>
       </c>
       <c r="I610" t="s">
         <v>219</v>
       </c>
       <c r="J610" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -38863,19 +38857,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
+        <v>3033</v>
+      </c>
+      <c r="G611" t="s">
         <v>3034</v>
       </c>
-      <c r="G611" t="s">
+      <c r="H611" t="s">
         <v>3035</v>
-      </c>
-      <c r="H611" t="s">
-        <v>3036</v>
       </c>
       <c r="I611" t="s">
         <v>219</v>
       </c>
       <c r="J611" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -38887,19 +38881,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
+        <v>3036</v>
+      </c>
+      <c r="G612" t="s">
         <v>3037</v>
       </c>
-      <c r="G612" t="s">
+      <c r="H612" t="s">
         <v>3038</v>
       </c>
-      <c r="H612" t="s">
+      <c r="I612" t="s">
         <v>3039</v>
       </c>
-      <c r="I612" t="s">
+      <c r="J612" t="s">
         <v>3040</v>
-      </c>
-      <c r="J612" t="s">
-        <v>3041</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -38911,19 +38905,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
+        <v>3041</v>
+      </c>
+      <c r="G613" t="s">
         <v>3042</v>
       </c>
-      <c r="G613" t="s">
+      <c r="H613" t="s">
         <v>3043</v>
-      </c>
-      <c r="H613" t="s">
-        <v>3044</v>
       </c>
       <c r="I613" t="s">
         <v>1388</v>
       </c>
       <c r="J613" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -38935,19 +38929,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
+        <v>3045</v>
+      </c>
+      <c r="G614" t="s">
         <v>3046</v>
       </c>
-      <c r="G614" t="s">
+      <c r="H614" t="s">
         <v>3047</v>
-      </c>
-      <c r="H614" t="s">
-        <v>3048</v>
       </c>
       <c r="I614" t="s">
         <v>399</v>
       </c>
       <c r="J614" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -38959,19 +38953,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
+        <v>3049</v>
+      </c>
+      <c r="G615" t="s">
         <v>3050</v>
       </c>
-      <c r="G615" t="s">
+      <c r="H615" t="s">
         <v>3051</v>
       </c>
-      <c r="H615" t="s">
+      <c r="I615" t="s">
         <v>3052</v>
       </c>
-      <c r="I615" t="s">
+      <c r="J615" t="s">
         <v>3053</v>
-      </c>
-      <c r="J615" t="s">
-        <v>3054</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -38983,19 +38977,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
+        <v>3054</v>
+      </c>
+      <c r="G616" t="s">
         <v>3055</v>
       </c>
-      <c r="G616" t="s">
+      <c r="H616" t="s">
         <v>3056</v>
-      </c>
-      <c r="H616" t="s">
-        <v>3057</v>
       </c>
       <c r="I616" t="s">
         <v>2250</v>
       </c>
       <c r="J616" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -39007,19 +39001,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
+        <v>3058</v>
+      </c>
+      <c r="G617" t="s">
         <v>3059</v>
       </c>
-      <c r="G617" t="s">
+      <c r="H617" t="s">
         <v>3060</v>
       </c>
-      <c r="H617" t="s">
+      <c r="I617" t="s">
         <v>3061</v>
       </c>
-      <c r="I617" t="s">
+      <c r="J617" t="s">
         <v>3062</v>
-      </c>
-      <c r="J617" t="s">
-        <v>3063</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -39031,19 +39025,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
+        <v>3063</v>
+      </c>
+      <c r="G618" t="s">
         <v>3064</v>
       </c>
-      <c r="G618" t="s">
+      <c r="H618" t="s">
         <v>3065</v>
-      </c>
-      <c r="H618" t="s">
-        <v>3066</v>
       </c>
       <c r="I618" t="s">
         <v>287</v>
       </c>
       <c r="J618" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -39055,19 +39049,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
+        <v>3067</v>
+      </c>
+      <c r="G619" t="s">
         <v>3068</v>
       </c>
-      <c r="G619" t="s">
+      <c r="H619" t="s">
         <v>3069</v>
-      </c>
-      <c r="H619" t="s">
-        <v>3070</v>
       </c>
       <c r="I619" t="s">
         <v>895</v>
       </c>
       <c r="J619" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -39079,19 +39073,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
+        <v>3071</v>
+      </c>
+      <c r="G620" t="s">
         <v>3072</v>
       </c>
-      <c r="G620" t="s">
+      <c r="H620" t="s">
         <v>3073</v>
       </c>
-      <c r="H620" t="s">
+      <c r="I620" t="s">
         <v>3074</v>
       </c>
-      <c r="I620" t="s">
+      <c r="J620" t="s">
         <v>3075</v>
-      </c>
-      <c r="J620" t="s">
-        <v>3076</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -39103,19 +39097,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
+        <v>3076</v>
+      </c>
+      <c r="G621" t="s">
         <v>3077</v>
       </c>
-      <c r="G621" t="s">
+      <c r="H621" t="s">
         <v>3078</v>
       </c>
-      <c r="H621" t="s">
+      <c r="I621" t="s">
         <v>3079</v>
       </c>
-      <c r="I621" t="s">
+      <c r="J621" t="s">
         <v>3080</v>
-      </c>
-      <c r="J621" t="s">
-        <v>3081</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -39127,19 +39121,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
+        <v>3081</v>
+      </c>
+      <c r="G622" t="s">
         <v>3082</v>
       </c>
-      <c r="G622" t="s">
+      <c r="H622" t="s">
         <v>3083</v>
-      </c>
-      <c r="H622" t="s">
-        <v>3084</v>
       </c>
       <c r="I622" t="s">
         <v>951</v>
       </c>
       <c r="J622" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -39151,19 +39145,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
+        <v>3085</v>
+      </c>
+      <c r="G623" t="s">
         <v>3086</v>
       </c>
-      <c r="G623" t="s">
+      <c r="H623" t="s">
         <v>3087</v>
       </c>
-      <c r="H623" t="s">
+      <c r="I623" t="s">
         <v>3088</v>
       </c>
-      <c r="I623" t="s">
+      <c r="J623" t="s">
         <v>3089</v>
-      </c>
-      <c r="J623" t="s">
-        <v>3090</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -39175,19 +39169,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
+        <v>3090</v>
+      </c>
+      <c r="G624" t="s">
         <v>3091</v>
       </c>
-      <c r="G624" t="s">
+      <c r="H624" t="s">
         <v>3092</v>
-      </c>
-      <c r="H624" t="s">
-        <v>3093</v>
       </c>
       <c r="I624" t="s">
         <v>1626</v>
       </c>
       <c r="J624" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -39199,19 +39193,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
+        <v>3094</v>
+      </c>
+      <c r="G625" t="s">
         <v>3095</v>
       </c>
-      <c r="G625" t="s">
+      <c r="H625" t="s">
         <v>3096</v>
-      </c>
-      <c r="H625" t="s">
-        <v>3097</v>
       </c>
       <c r="I625" t="s">
         <v>1218</v>
       </c>
       <c r="J625" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -39223,19 +39217,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
+        <v>3098</v>
+      </c>
+      <c r="G626" t="s">
         <v>3099</v>
       </c>
-      <c r="G626" t="s">
+      <c r="H626" t="s">
         <v>3100</v>
       </c>
-      <c r="H626" t="s">
+      <c r="I626" t="s">
         <v>3101</v>
       </c>
-      <c r="I626" t="s">
+      <c r="J626" t="s">
         <v>3102</v>
-      </c>
-      <c r="J626" t="s">
-        <v>3103</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -39247,19 +39241,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
+        <v>3103</v>
+      </c>
+      <c r="G627" t="s">
         <v>3104</v>
       </c>
-      <c r="G627" t="s">
+      <c r="H627" t="s">
         <v>3105</v>
-      </c>
-      <c r="H627" t="s">
-        <v>3106</v>
       </c>
       <c r="I627" t="s">
         <v>123</v>
       </c>
       <c r="J627" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -39271,19 +39265,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
+        <v>3107</v>
+      </c>
+      <c r="G628" t="s">
         <v>3108</v>
       </c>
-      <c r="G628" t="s">
+      <c r="H628" t="s">
         <v>3109</v>
-      </c>
-      <c r="H628" t="s">
-        <v>3110</v>
       </c>
       <c r="I628" t="s">
         <v>895</v>
       </c>
       <c r="J628" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -39295,19 +39289,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
+        <v>3111</v>
+      </c>
+      <c r="G629" t="s">
         <v>3112</v>
       </c>
-      <c r="G629" t="s">
+      <c r="H629" t="s">
         <v>3113</v>
-      </c>
-      <c r="H629" t="s">
-        <v>3114</v>
       </c>
       <c r="I629" t="s">
         <v>1626</v>
       </c>
       <c r="J629" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -39319,19 +39313,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
+        <v>3115</v>
+      </c>
+      <c r="G630" t="s">
         <v>3116</v>
       </c>
-      <c r="G630" t="s">
+      <c r="H630" t="s">
         <v>3117</v>
-      </c>
-      <c r="H630" t="s">
-        <v>3118</v>
       </c>
       <c r="I630" t="s">
         <v>677</v>
       </c>
       <c r="J630" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -39343,19 +39337,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
+        <v>3119</v>
+      </c>
+      <c r="G631" t="s">
         <v>3120</v>
       </c>
-      <c r="G631" t="s">
+      <c r="H631" t="s">
         <v>3121</v>
       </c>
-      <c r="H631" t="s">
+      <c r="I631" t="s">
+        <v>2787</v>
+      </c>
+      <c r="J631" t="s">
         <v>3122</v>
-      </c>
-      <c r="I631" t="s">
-        <v>2788</v>
-      </c>
-      <c r="J631" t="s">
-        <v>3123</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -39367,19 +39361,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
+        <v>3123</v>
+      </c>
+      <c r="G632" t="s">
         <v>3124</v>
       </c>
-      <c r="G632" t="s">
+      <c r="H632" t="s">
         <v>3125</v>
       </c>
-      <c r="H632" t="s">
+      <c r="I632" t="s">
         <v>3126</v>
       </c>
-      <c r="I632" t="s">
+      <c r="J632" t="s">
         <v>3127</v>
-      </c>
-      <c r="J632" t="s">
-        <v>3128</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -39391,19 +39385,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
+        <v>3128</v>
+      </c>
+      <c r="G633" t="s">
         <v>3129</v>
       </c>
-      <c r="G633" t="s">
+      <c r="H633" t="s">
         <v>3130</v>
       </c>
-      <c r="H633" t="s">
+      <c r="I633" t="s">
         <v>3131</v>
       </c>
-      <c r="I633" t="s">
+      <c r="J633" t="s">
         <v>3132</v>
-      </c>
-      <c r="J633" t="s">
-        <v>3133</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -39415,19 +39409,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
+        <v>3133</v>
+      </c>
+      <c r="G634" t="s">
         <v>3134</v>
       </c>
-      <c r="G634" t="s">
+      <c r="H634" t="s">
         <v>3135</v>
-      </c>
-      <c r="H634" t="s">
-        <v>3136</v>
       </c>
       <c r="I634" t="s">
         <v>219</v>
       </c>
       <c r="J634" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -39439,19 +39433,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
+        <v>3137</v>
+      </c>
+      <c r="G635" t="s">
         <v>3138</v>
       </c>
-      <c r="G635" t="s">
+      <c r="H635" t="s">
         <v>3139</v>
-      </c>
-      <c r="H635" t="s">
-        <v>3140</v>
       </c>
       <c r="I635" t="s">
         <v>809</v>
       </c>
       <c r="J635" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -39463,19 +39457,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
+        <v>3141</v>
+      </c>
+      <c r="G636" t="s">
         <v>3142</v>
       </c>
-      <c r="G636" t="s">
+      <c r="H636" t="s">
         <v>3143</v>
       </c>
-      <c r="H636" t="s">
+      <c r="I636" t="s">
         <v>3144</v>
       </c>
-      <c r="I636" t="s">
+      <c r="J636" t="s">
         <v>3145</v>
-      </c>
-      <c r="J636" t="s">
-        <v>3146</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -39487,19 +39481,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
+        <v>3146</v>
+      </c>
+      <c r="G637" t="s">
         <v>3147</v>
       </c>
-      <c r="G637" t="s">
+      <c r="H637" t="s">
         <v>3148</v>
-      </c>
-      <c r="H637" t="s">
-        <v>3149</v>
       </c>
       <c r="I637" t="s">
         <v>287</v>
       </c>
       <c r="J637" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -39511,19 +39505,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
+        <v>3150</v>
+      </c>
+      <c r="G638" t="s">
         <v>3151</v>
       </c>
-      <c r="G638" t="s">
+      <c r="H638" t="s">
         <v>3152</v>
-      </c>
-      <c r="H638" t="s">
-        <v>3153</v>
       </c>
       <c r="I638" t="s">
         <v>287</v>
       </c>
       <c r="J638" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -39535,19 +39529,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
+        <v>3154</v>
+      </c>
+      <c r="G639" t="s">
         <v>3155</v>
       </c>
-      <c r="G639" t="s">
+      <c r="H639" t="s">
         <v>3156</v>
       </c>
-      <c r="H639" t="s">
+      <c r="I639" t="s">
         <v>3157</v>
       </c>
-      <c r="I639" t="s">
+      <c r="J639" t="s">
         <v>3158</v>
-      </c>
-      <c r="J639" t="s">
-        <v>3159</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -39559,19 +39553,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
+        <v>3159</v>
+      </c>
+      <c r="G640" t="s">
         <v>3160</v>
       </c>
-      <c r="G640" t="s">
+      <c r="H640" t="s">
         <v>3161</v>
-      </c>
-      <c r="H640" t="s">
-        <v>3162</v>
       </c>
       <c r="I640" t="s">
         <v>219</v>
       </c>
       <c r="J640" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -39583,19 +39577,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
+        <v>3163</v>
+      </c>
+      <c r="G641" t="s">
         <v>3164</v>
       </c>
-      <c r="G641" t="s">
+      <c r="H641" t="s">
         <v>3165</v>
-      </c>
-      <c r="H641" t="s">
-        <v>3166</v>
       </c>
       <c r="I641" t="s">
         <v>1524</v>
       </c>
       <c r="J641" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -39607,19 +39601,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
+        <v>3167</v>
+      </c>
+      <c r="G642" t="s">
         <v>3168</v>
       </c>
-      <c r="G642" t="s">
+      <c r="H642" t="s">
         <v>3169</v>
-      </c>
-      <c r="H642" t="s">
-        <v>3170</v>
       </c>
       <c r="I642" t="s">
         <v>534</v>
       </c>
       <c r="J642" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -39631,19 +39625,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
+        <v>3171</v>
+      </c>
+      <c r="G643" t="s">
         <v>3172</v>
       </c>
-      <c r="G643" t="s">
+      <c r="H643" t="s">
         <v>3173</v>
-      </c>
-      <c r="H643" t="s">
-        <v>3174</v>
       </c>
       <c r="I643" t="s">
         <v>142</v>
       </c>
       <c r="J643" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -39655,19 +39649,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
+        <v>3175</v>
+      </c>
+      <c r="G644" t="s">
         <v>3176</v>
       </c>
-      <c r="G644" t="s">
+      <c r="H644" t="s">
         <v>3177</v>
       </c>
-      <c r="H644" t="s">
+      <c r="I644" t="s">
         <v>3178</v>
       </c>
-      <c r="I644" t="s">
+      <c r="J644" t="s">
         <v>3179</v>
-      </c>
-      <c r="J644" t="s">
-        <v>3180</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -39679,19 +39673,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G645" t="s">
         <v>3181</v>
       </c>
-      <c r="G645" t="s">
+      <c r="H645" t="s">
         <v>3182</v>
-      </c>
-      <c r="H645" t="s">
-        <v>3183</v>
       </c>
       <c r="I645" t="s">
         <v>1284</v>
       </c>
       <c r="J645" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -39703,19 +39697,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
+        <v>3184</v>
+      </c>
+      <c r="G646" t="s">
         <v>3185</v>
       </c>
-      <c r="G646" t="s">
+      <c r="H646" t="s">
         <v>3186</v>
       </c>
-      <c r="H646" t="s">
+      <c r="I646" t="s">
+        <v>2288</v>
+      </c>
+      <c r="J646" t="s">
         <v>3187</v>
-      </c>
-      <c r="I646" t="s">
-        <v>2289</v>
-      </c>
-      <c r="J646" t="s">
-        <v>3188</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -39727,19 +39721,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
+        <v>3188</v>
+      </c>
+      <c r="G647" t="s">
         <v>3189</v>
       </c>
-      <c r="G647" t="s">
+      <c r="H647" t="s">
         <v>3190</v>
-      </c>
-      <c r="H647" t="s">
-        <v>3191</v>
       </c>
       <c r="I647" t="s">
         <v>287</v>
       </c>
       <c r="J647" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -39751,19 +39745,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
+        <v>3192</v>
+      </c>
+      <c r="G648" t="s">
         <v>3193</v>
       </c>
-      <c r="G648" t="s">
+      <c r="H648" t="s">
         <v>3194</v>
-      </c>
-      <c r="H648" t="s">
-        <v>3195</v>
       </c>
       <c r="I648" t="s">
         <v>1626</v>
       </c>
       <c r="J648" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -39775,19 +39769,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
+        <v>3196</v>
+      </c>
+      <c r="G649" t="s">
         <v>3197</v>
       </c>
-      <c r="G649" t="s">
+      <c r="H649" t="s">
         <v>3198</v>
-      </c>
-      <c r="H649" t="s">
-        <v>3199</v>
       </c>
       <c r="I649" t="s">
         <v>399</v>
       </c>
       <c r="J649" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -39799,19 +39793,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
+        <v>3200</v>
+      </c>
+      <c r="G650" t="s">
         <v>3201</v>
       </c>
-      <c r="G650" t="s">
+      <c r="H650" t="s">
         <v>3202</v>
       </c>
-      <c r="H650" t="s">
+      <c r="I650" t="s">
+        <v>2638</v>
+      </c>
+      <c r="J650" t="s">
         <v>3203</v>
-      </c>
-      <c r="I650" t="s">
-        <v>2639</v>
-      </c>
-      <c r="J650" t="s">
-        <v>3204</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -39823,19 +39817,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
+        <v>3204</v>
+      </c>
+      <c r="G651" t="s">
         <v>3205</v>
       </c>
-      <c r="G651" t="s">
+      <c r="H651" t="s">
         <v>3206</v>
       </c>
-      <c r="H651" t="s">
+      <c r="I651" t="s">
         <v>3207</v>
       </c>
-      <c r="I651" t="s">
+      <c r="J651" t="s">
         <v>3208</v>
-      </c>
-      <c r="J651" t="s">
-        <v>3209</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -39847,19 +39841,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
+        <v>3209</v>
+      </c>
+      <c r="G652" t="s">
         <v>3210</v>
       </c>
-      <c r="G652" t="s">
+      <c r="H652" t="s">
         <v>3211</v>
-      </c>
-      <c r="H652" t="s">
-        <v>3212</v>
       </c>
       <c r="I652" t="s">
         <v>1310</v>
       </c>
       <c r="J652" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -39871,19 +39865,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
+        <v>3213</v>
+      </c>
+      <c r="G653" t="s">
         <v>3214</v>
       </c>
-      <c r="G653" t="s">
+      <c r="H653" t="s">
         <v>3215</v>
       </c>
-      <c r="H653" t="s">
+      <c r="I653" t="s">
         <v>3216</v>
       </c>
-      <c r="I653" t="s">
+      <c r="J653" t="s">
         <v>3217</v>
-      </c>
-      <c r="J653" t="s">
-        <v>3218</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -39895,19 +39889,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
+        <v>3218</v>
+      </c>
+      <c r="G654" t="s">
         <v>3219</v>
       </c>
-      <c r="G654" t="s">
+      <c r="H654" t="s">
         <v>3220</v>
       </c>
-      <c r="H654" t="s">
+      <c r="I654" t="s">
         <v>3221</v>
       </c>
-      <c r="I654" t="s">
+      <c r="J654" t="s">
         <v>3222</v>
-      </c>
-      <c r="J654" t="s">
-        <v>3223</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -39919,19 +39913,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
+        <v>3223</v>
+      </c>
+      <c r="G655" t="s">
         <v>3224</v>
       </c>
-      <c r="G655" t="s">
+      <c r="H655" t="s">
         <v>3225</v>
       </c>
-      <c r="H655" t="s">
+      <c r="I655" t="s">
         <v>3226</v>
       </c>
-      <c r="I655" t="s">
+      <c r="J655" t="s">
         <v>3227</v>
-      </c>
-      <c r="J655" t="s">
-        <v>3228</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -39943,19 +39937,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
+        <v>3228</v>
+      </c>
+      <c r="G656" t="s">
         <v>3229</v>
       </c>
-      <c r="G656" t="s">
+      <c r="H656" t="s">
         <v>3230</v>
-      </c>
-      <c r="H656" t="s">
-        <v>3231</v>
       </c>
       <c r="I656" t="s">
         <v>677</v>
       </c>
       <c r="J656" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -39967,19 +39961,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
+        <v>3232</v>
+      </c>
+      <c r="G657" t="s">
         <v>3233</v>
       </c>
-      <c r="G657" t="s">
+      <c r="H657" t="s">
         <v>3234</v>
-      </c>
-      <c r="H657" t="s">
-        <v>3235</v>
       </c>
       <c r="I657" t="s">
         <v>2030</v>
       </c>
       <c r="J657" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -39991,19 +39985,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
+        <v>3236</v>
+      </c>
+      <c r="G658" t="s">
         <v>3237</v>
       </c>
-      <c r="G658" t="s">
+      <c r="H658" t="s">
         <v>3238</v>
       </c>
-      <c r="H658" t="s">
+      <c r="I658" t="s">
+        <v>2852</v>
+      </c>
+      <c r="J658" t="s">
         <v>3239</v>
-      </c>
-      <c r="I658" t="s">
-        <v>2853</v>
-      </c>
-      <c r="J658" t="s">
-        <v>3240</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -40015,19 +40009,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
+        <v>3240</v>
+      </c>
+      <c r="G659" t="s">
         <v>3241</v>
       </c>
-      <c r="G659" t="s">
+      <c r="H659" t="s">
         <v>3242</v>
-      </c>
-      <c r="H659" t="s">
-        <v>3243</v>
       </c>
       <c r="I659" t="s">
         <v>1960</v>
       </c>
       <c r="J659" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -40039,19 +40033,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
+        <v>3244</v>
+      </c>
+      <c r="G660" t="s">
         <v>3245</v>
       </c>
-      <c r="G660" t="s">
+      <c r="H660" t="s">
         <v>3246</v>
-      </c>
-      <c r="H660" t="s">
-        <v>3247</v>
       </c>
       <c r="I660" t="s">
         <v>49</v>
       </c>
       <c r="J660" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -40063,19 +40057,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
+        <v>3248</v>
+      </c>
+      <c r="G661" t="s">
         <v>3249</v>
       </c>
-      <c r="G661" t="s">
+      <c r="H661" t="s">
         <v>3250</v>
-      </c>
-      <c r="H661" t="s">
-        <v>3251</v>
       </c>
       <c r="I661" t="s">
         <v>649</v>
       </c>
       <c r="J661" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -40087,19 +40081,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
+        <v>3252</v>
+      </c>
+      <c r="G662" t="s">
         <v>3253</v>
       </c>
-      <c r="G662" t="s">
+      <c r="H662" t="s">
         <v>3254</v>
       </c>
-      <c r="H662" t="s">
+      <c r="I662" t="s">
+        <v>2839</v>
+      </c>
+      <c r="J662" t="s">
         <v>3255</v>
-      </c>
-      <c r="I662" t="s">
-        <v>2840</v>
-      </c>
-      <c r="J662" t="s">
-        <v>3256</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -40111,19 +40105,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
+        <v>3256</v>
+      </c>
+      <c r="G663" t="s">
         <v>3257</v>
       </c>
-      <c r="G663" t="s">
+      <c r="H663" t="s">
         <v>3258</v>
       </c>
-      <c r="H663" t="s">
+      <c r="I663" t="s">
+        <v>3014</v>
+      </c>
+      <c r="J663" t="s">
         <v>3259</v>
-      </c>
-      <c r="I663" t="s">
-        <v>3015</v>
-      </c>
-      <c r="J663" t="s">
-        <v>3260</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -40135,19 +40129,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
+        <v>3260</v>
+      </c>
+      <c r="G664" t="s">
         <v>3261</v>
       </c>
-      <c r="G664" t="s">
+      <c r="H664" t="s">
         <v>3262</v>
-      </c>
-      <c r="H664" t="s">
-        <v>3263</v>
       </c>
       <c r="I664" t="s">
         <v>399</v>
       </c>
       <c r="J664" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -40159,19 +40153,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
+        <v>3264</v>
+      </c>
+      <c r="G665" t="s">
         <v>3265</v>
       </c>
-      <c r="G665" t="s">
+      <c r="H665" t="s">
         <v>3266</v>
       </c>
-      <c r="H665" t="s">
+      <c r="I665" t="s">
         <v>3267</v>
       </c>
-      <c r="I665" t="s">
+      <c r="J665" t="s">
         <v>3268</v>
-      </c>
-      <c r="J665" t="s">
-        <v>3269</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -40183,19 +40177,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
+        <v>3269</v>
+      </c>
+      <c r="G666" t="s">
         <v>3270</v>
       </c>
-      <c r="G666" t="s">
+      <c r="H666" t="s">
         <v>3271</v>
-      </c>
-      <c r="H666" t="s">
-        <v>3272</v>
       </c>
       <c r="I666" t="s">
         <v>1388</v>
       </c>
       <c r="J666" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -40207,19 +40201,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
+        <v>3273</v>
+      </c>
+      <c r="G667" t="s">
         <v>3274</v>
       </c>
-      <c r="G667" t="s">
+      <c r="H667" t="s">
         <v>3275</v>
-      </c>
-      <c r="H667" t="s">
-        <v>3276</v>
       </c>
       <c r="I667" t="s">
         <v>449</v>
       </c>
       <c r="J667" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -40231,19 +40225,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
+        <v>3277</v>
+      </c>
+      <c r="G668" t="s">
         <v>3278</v>
       </c>
-      <c r="G668" t="s">
+      <c r="H668" t="s">
         <v>3279</v>
       </c>
-      <c r="H668" t="s">
+      <c r="I668" t="s">
         <v>3280</v>
       </c>
-      <c r="I668" t="s">
+      <c r="J668" t="s">
         <v>3281</v>
-      </c>
-      <c r="J668" t="s">
-        <v>3282</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -40255,19 +40249,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
+        <v>3282</v>
+      </c>
+      <c r="G669" t="s">
         <v>3283</v>
       </c>
-      <c r="G669" t="s">
+      <c r="H669" t="s">
         <v>3284</v>
-      </c>
-      <c r="H669" t="s">
-        <v>3285</v>
       </c>
       <c r="I669" t="s">
         <v>416</v>
       </c>
       <c r="J669" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -40279,19 +40273,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
+        <v>3286</v>
+      </c>
+      <c r="G670" t="s">
         <v>3287</v>
       </c>
-      <c r="G670" t="s">
+      <c r="H670" t="s">
         <v>3288</v>
       </c>
-      <c r="H670" t="s">
+      <c r="I670" t="s">
         <v>3289</v>
       </c>
-      <c r="I670" t="s">
+      <c r="J670" t="s">
         <v>3290</v>
-      </c>
-      <c r="J670" t="s">
-        <v>3291</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -40303,19 +40297,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
+        <v>3291</v>
+      </c>
+      <c r="G671" t="s">
         <v>3292</v>
       </c>
-      <c r="G671" t="s">
+      <c r="H671" t="s">
         <v>3293</v>
-      </c>
-      <c r="H671" t="s">
-        <v>3294</v>
       </c>
       <c r="I671" t="s">
         <v>2211</v>
       </c>
       <c r="J671" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -40327,19 +40321,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
+        <v>3295</v>
+      </c>
+      <c r="G672" t="s">
         <v>3296</v>
       </c>
-      <c r="G672" t="s">
+      <c r="H672" t="s">
         <v>3297</v>
-      </c>
-      <c r="H672" t="s">
-        <v>3298</v>
       </c>
       <c r="I672" t="s">
         <v>123</v>
       </c>
       <c r="J672" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -40351,19 +40345,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
+        <v>3299</v>
+      </c>
+      <c r="G673" t="s">
         <v>3300</v>
       </c>
-      <c r="G673" t="s">
+      <c r="H673" t="s">
         <v>3301</v>
-      </c>
-      <c r="H673" t="s">
-        <v>3302</v>
       </c>
       <c r="I673" t="s">
         <v>1454</v>
       </c>
       <c r="J673" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -40375,19 +40369,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
+        <v>3303</v>
+      </c>
+      <c r="G674" t="s">
         <v>3304</v>
       </c>
-      <c r="G674" t="s">
+      <c r="H674" t="s">
         <v>3305</v>
       </c>
-      <c r="H674" t="s">
+      <c r="I674" t="s">
+        <v>3280</v>
+      </c>
+      <c r="J674" t="s">
         <v>3306</v>
-      </c>
-      <c r="I674" t="s">
-        <v>3281</v>
-      </c>
-      <c r="J674" t="s">
-        <v>3307</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -40399,19 +40393,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
+        <v>3307</v>
+      </c>
+      <c r="G675" t="s">
         <v>3308</v>
       </c>
-      <c r="G675" t="s">
+      <c r="H675" t="s">
         <v>3309</v>
       </c>
-      <c r="H675" t="s">
+      <c r="I675" t="s">
         <v>3310</v>
       </c>
-      <c r="I675" t="s">
+      <c r="J675" t="s">
         <v>3311</v>
-      </c>
-      <c r="J675" t="s">
-        <v>3312</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -40423,19 +40417,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
+        <v>3312</v>
+      </c>
+      <c r="G676" t="s">
         <v>3313</v>
       </c>
-      <c r="G676" t="s">
+      <c r="H676" t="s">
         <v>3314</v>
-      </c>
-      <c r="H676" t="s">
-        <v>3315</v>
       </c>
       <c r="I676" t="s">
         <v>1648</v>
       </c>
       <c r="J676" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -40447,19 +40441,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G677" t="s">
         <v>3317</v>
       </c>
-      <c r="G677" t="s">
+      <c r="H677" t="s">
         <v>3318</v>
-      </c>
-      <c r="H677" t="s">
-        <v>3319</v>
       </c>
       <c r="I677" t="s">
         <v>671</v>
       </c>
       <c r="J677" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -40471,19 +40465,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
+        <v>3320</v>
+      </c>
+      <c r="G678" t="s">
         <v>3321</v>
       </c>
-      <c r="G678" t="s">
+      <c r="H678" t="s">
         <v>3322</v>
-      </c>
-      <c r="H678" t="s">
-        <v>3323</v>
       </c>
       <c r="I678" t="s">
         <v>399</v>
       </c>
       <c r="J678" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -40495,19 +40489,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
+        <v>3324</v>
+      </c>
+      <c r="G679" t="s">
         <v>3325</v>
       </c>
-      <c r="G679" t="s">
+      <c r="H679" t="s">
         <v>3326</v>
-      </c>
-      <c r="H679" t="s">
-        <v>3327</v>
       </c>
       <c r="I679" t="s">
         <v>49</v>
       </c>
       <c r="J679" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -40519,19 +40513,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
+        <v>3328</v>
+      </c>
+      <c r="G680" t="s">
         <v>3329</v>
       </c>
-      <c r="G680" t="s">
+      <c r="H680" t="s">
         <v>3330</v>
       </c>
-      <c r="H680" t="s">
+      <c r="I680" t="s">
         <v>3331</v>
       </c>
-      <c r="I680" t="s">
+      <c r="J680" t="s">
         <v>3332</v>
-      </c>
-      <c r="J680" t="s">
-        <v>3333</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -40543,19 +40537,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
+        <v>3333</v>
+      </c>
+      <c r="G681" t="s">
         <v>3334</v>
       </c>
-      <c r="G681" t="s">
+      <c r="H681" t="s">
         <v>3335</v>
-      </c>
-      <c r="H681" t="s">
-        <v>3336</v>
       </c>
       <c r="I681" t="s">
         <v>230</v>
       </c>
       <c r="J681" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -40567,19 +40561,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
+        <v>3337</v>
+      </c>
+      <c r="G682" t="s">
         <v>3338</v>
       </c>
-      <c r="G682" t="s">
+      <c r="H682" t="s">
         <v>3339</v>
-      </c>
-      <c r="H682" t="s">
-        <v>3340</v>
       </c>
       <c r="I682" t="s">
         <v>1057</v>
       </c>
       <c r="J682" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -40591,19 +40585,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
+        <v>3341</v>
+      </c>
+      <c r="G683" t="s">
         <v>3342</v>
       </c>
-      <c r="G683" t="s">
+      <c r="H683" t="s">
         <v>3343</v>
-      </c>
-      <c r="H683" t="s">
-        <v>3344</v>
       </c>
       <c r="I683" t="s">
         <v>230</v>
       </c>
       <c r="J683" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -40615,19 +40609,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
+        <v>3345</v>
+      </c>
+      <c r="G684" t="s">
         <v>3346</v>
       </c>
-      <c r="G684" t="s">
+      <c r="H684" t="s">
         <v>3347</v>
-      </c>
-      <c r="H684" t="s">
-        <v>3348</v>
       </c>
       <c r="I684" t="s">
         <v>803</v>
       </c>
       <c r="J684" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -40639,19 +40633,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
+        <v>3349</v>
+      </c>
+      <c r="G685" t="s">
         <v>3350</v>
       </c>
-      <c r="G685" t="s">
+      <c r="H685" t="s">
         <v>3351</v>
-      </c>
-      <c r="H685" t="s">
-        <v>3352</v>
       </c>
       <c r="I685" t="s">
         <v>405</v>
       </c>
       <c r="J685" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -40663,19 +40657,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
+        <v>3353</v>
+      </c>
+      <c r="G686" t="s">
         <v>3354</v>
       </c>
-      <c r="G686" t="s">
+      <c r="H686" t="s">
         <v>3355</v>
       </c>
-      <c r="H686" t="s">
+      <c r="I686" t="s">
         <v>3356</v>
       </c>
-      <c r="I686" t="s">
+      <c r="J686" t="s">
         <v>3357</v>
-      </c>
-      <c r="J686" t="s">
-        <v>3358</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -40687,19 +40681,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
+        <v>3358</v>
+      </c>
+      <c r="G687" t="s">
         <v>3359</v>
       </c>
-      <c r="G687" t="s">
+      <c r="H687" t="s">
         <v>3360</v>
-      </c>
-      <c r="H687" t="s">
-        <v>3361</v>
       </c>
       <c r="I687" t="s">
         <v>1901</v>
       </c>
       <c r="J687" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -40711,19 +40705,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
+        <v>3362</v>
+      </c>
+      <c r="G688" t="s">
         <v>3363</v>
       </c>
-      <c r="G688" t="s">
+      <c r="H688" t="s">
         <v>3364</v>
       </c>
-      <c r="H688" t="s">
+      <c r="I688" t="s">
         <v>3365</v>
       </c>
-      <c r="I688" t="s">
+      <c r="J688" t="s">
         <v>3366</v>
-      </c>
-      <c r="J688" t="s">
-        <v>3367</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -40735,19 +40729,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G689" t="s">
         <v>3368</v>
       </c>
-      <c r="G689" t="s">
+      <c r="H689" t="s">
         <v>3369</v>
       </c>
-      <c r="H689" t="s">
+      <c r="I689" t="s">
         <v>3370</v>
       </c>
-      <c r="I689" t="s">
+      <c r="J689" t="s">
         <v>3371</v>
-      </c>
-      <c r="J689" t="s">
-        <v>3372</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -40759,19 +40753,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
+        <v>3372</v>
+      </c>
+      <c r="G690" t="s">
         <v>3373</v>
       </c>
-      <c r="G690" t="s">
+      <c r="H690" t="s">
         <v>3374</v>
-      </c>
-      <c r="H690" t="s">
-        <v>3375</v>
       </c>
       <c r="I690" t="s">
         <v>393</v>
       </c>
       <c r="J690" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -40783,19 +40777,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
+        <v>3376</v>
+      </c>
+      <c r="G691" t="s">
         <v>3377</v>
       </c>
-      <c r="G691" t="s">
+      <c r="H691" t="s">
         <v>3378</v>
-      </c>
-      <c r="H691" t="s">
-        <v>3379</v>
       </c>
       <c r="I691" t="s">
         <v>2019</v>
       </c>
       <c r="J691" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -40807,19 +40801,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
+        <v>3380</v>
+      </c>
+      <c r="G692" t="s">
         <v>3381</v>
       </c>
-      <c r="G692" t="s">
+      <c r="H692" t="s">
         <v>3382</v>
       </c>
-      <c r="H692" t="s">
+      <c r="I692" t="s">
         <v>3383</v>
       </c>
-      <c r="I692" t="s">
+      <c r="J692" t="s">
         <v>3384</v>
-      </c>
-      <c r="J692" t="s">
-        <v>3385</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -40831,19 +40825,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
+        <v>3385</v>
+      </c>
+      <c r="G693" t="s">
         <v>3386</v>
       </c>
-      <c r="G693" t="s">
+      <c r="H693" t="s">
         <v>3387</v>
-      </c>
-      <c r="H693" t="s">
-        <v>3388</v>
       </c>
       <c r="I693" t="s">
         <v>230</v>
       </c>
       <c r="J693" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -40855,19 +40849,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
+        <v>3389</v>
+      </c>
+      <c r="G694" t="s">
         <v>3390</v>
       </c>
-      <c r="G694" t="s">
+      <c r="H694" t="s">
         <v>3391</v>
-      </c>
-      <c r="H694" t="s">
-        <v>3392</v>
       </c>
       <c r="I694" t="s">
         <v>951</v>
       </c>
       <c r="J694" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -40879,19 +40873,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
+        <v>3393</v>
+      </c>
+      <c r="G695" t="s">
         <v>3394</v>
       </c>
-      <c r="G695" t="s">
+      <c r="H695" t="s">
         <v>3395</v>
-      </c>
-      <c r="H695" t="s">
-        <v>3396</v>
       </c>
       <c r="I695" t="s">
         <v>1901</v>
       </c>
       <c r="J695" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -40903,19 +40897,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
+        <v>3397</v>
+      </c>
+      <c r="G696" t="s">
         <v>3398</v>
       </c>
-      <c r="G696" t="s">
+      <c r="H696" t="s">
         <v>3399</v>
-      </c>
-      <c r="H696" t="s">
-        <v>3400</v>
       </c>
       <c r="I696" t="s">
         <v>951</v>
       </c>
       <c r="J696" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -40927,19 +40921,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
+        <v>3401</v>
+      </c>
+      <c r="G697" t="s">
         <v>3402</v>
       </c>
-      <c r="G697" t="s">
+      <c r="H697" t="s">
         <v>3403</v>
-      </c>
-      <c r="H697" t="s">
-        <v>3404</v>
       </c>
       <c r="I697" t="s">
         <v>1436</v>
       </c>
       <c r="J697" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -40951,19 +40945,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
+        <v>3405</v>
+      </c>
+      <c r="G698" t="s">
         <v>3406</v>
       </c>
-      <c r="G698" t="s">
+      <c r="H698" t="s">
         <v>3407</v>
-      </c>
-      <c r="H698" t="s">
-        <v>3408</v>
       </c>
       <c r="I698" t="s">
         <v>709</v>
       </c>
       <c r="J698" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -40975,19 +40969,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
+        <v>3409</v>
+      </c>
+      <c r="G699" t="s">
         <v>3410</v>
       </c>
-      <c r="G699" t="s">
+      <c r="H699" t="s">
         <v>3411</v>
       </c>
-      <c r="H699" t="s">
+      <c r="I699" t="s">
+        <v>3289</v>
+      </c>
+      <c r="J699" t="s">
         <v>3412</v>
-      </c>
-      <c r="I699" t="s">
-        <v>3290</v>
-      </c>
-      <c r="J699" t="s">
-        <v>3413</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -40999,19 +40993,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
+        <v>3413</v>
+      </c>
+      <c r="G700" t="s">
         <v>3414</v>
       </c>
-      <c r="G700" t="s">
+      <c r="H700" t="s">
         <v>3415</v>
-      </c>
-      <c r="H700" t="s">
-        <v>3416</v>
       </c>
       <c r="I700" t="s">
         <v>895</v>
       </c>
       <c r="J700" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -41023,19 +41017,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
+        <v>3417</v>
+      </c>
+      <c r="G701" t="s">
         <v>3418</v>
       </c>
-      <c r="G701" t="s">
+      <c r="H701" t="s">
         <v>3419</v>
       </c>
-      <c r="H701" t="s">
+      <c r="I701" t="s">
         <v>3420</v>
       </c>
-      <c r="I701" t="s">
+      <c r="J701" t="s">
         <v>3421</v>
-      </c>
-      <c r="J701" t="s">
-        <v>3422</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -41047,19 +41041,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
+        <v>3422</v>
+      </c>
+      <c r="G702" t="s">
         <v>3423</v>
       </c>
-      <c r="G702" t="s">
+      <c r="H702" t="s">
         <v>3424</v>
-      </c>
-      <c r="H702" t="s">
-        <v>3425</v>
       </c>
       <c r="I702" t="s">
         <v>895</v>
       </c>
       <c r="J702" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -41071,19 +41065,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
+        <v>3426</v>
+      </c>
+      <c r="G703" t="s">
         <v>3427</v>
       </c>
-      <c r="G703" t="s">
+      <c r="H703" t="s">
         <v>3428</v>
       </c>
-      <c r="H703" t="s">
+      <c r="I703" t="s">
         <v>3429</v>
       </c>
-      <c r="I703" t="s">
+      <c r="J703" t="s">
         <v>3430</v>
-      </c>
-      <c r="J703" t="s">
-        <v>3431</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -41095,19 +41089,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
+        <v>3431</v>
+      </c>
+      <c r="G704" t="s">
         <v>3432</v>
       </c>
-      <c r="G704" t="s">
+      <c r="H704" t="s">
         <v>3433</v>
-      </c>
-      <c r="H704" t="s">
-        <v>3434</v>
       </c>
       <c r="I704" t="s">
         <v>49</v>
       </c>
       <c r="J704" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="K704">
         <v>2001</v>
